--- a/Sales_Report.xlsx
+++ b/Sales_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardobazua/bza-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A5DB15-2C95-5642-98D8-7571C5D0827D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1C2C7B-5645-834D-B675-B9049519E079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="820" windowWidth="30240" windowHeight="17480" xr2:uid="{A69E99B4-FD75-534F-A443-AF5D6F49D11E}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="30240" windowHeight="17480" xr2:uid="{A69E99B4-FD75-534F-A443-AF5D6F49D11E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -7058,12 +7058,11 @@
       </c>
       <c r="U67" s="28"/>
       <c r="V67" s="42">
-        <f>SUM(R67:T67)</f>
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="W67" s="28">
         <f>O67*V67</f>
-        <v>339410.24</v>
+        <v>323053.12</v>
       </c>
       <c r="X67" s="28">
         <v>705</v>
@@ -7084,7 +7083,7 @@
       </c>
       <c r="AD67" s="28">
         <f>AC67-W67</f>
-        <v>20957.560000000056</v>
+        <v>37314.680000000051</v>
       </c>
       <c r="AE67" t="s">
         <v>82</v>
@@ -7142,12 +7141,11 @@
       </c>
       <c r="U68" s="28"/>
       <c r="V68" s="42">
-        <f>SUM(R68:T68)</f>
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="W68" s="28">
         <f>O68*V68</f>
-        <v>338104.81599999999</v>
+        <v>321810.60800000001</v>
       </c>
       <c r="X68" s="28">
         <v>705</v>
@@ -7168,7 +7166,7 @@
       </c>
       <c r="AD68" s="28">
         <f>AC68-W68</f>
-        <v>20876.954000000027</v>
+        <v>37171.162000000011</v>
       </c>
       <c r="AE68" s="17"/>
     </row>
@@ -7224,12 +7222,11 @@
       </c>
       <c r="U69" s="28"/>
       <c r="V69" s="42">
-        <f>SUM(R69:T69)</f>
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="W69" s="28">
         <f>O69*V69</f>
-        <v>322061.91200000001</v>
+        <v>306540.85600000003</v>
       </c>
       <c r="X69" s="28">
         <v>705</v>
@@ -7250,7 +7247,7 @@
       </c>
       <c r="AD69" s="28">
         <f t="shared" ref="AD69:AD73" si="31">AC69-W69</f>
-        <v>19886.353000000003</v>
+        <v>35407.408999999985</v>
       </c>
     </row>
     <row r="70" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -7305,12 +7302,11 @@
       </c>
       <c r="U70" s="28"/>
       <c r="V70" s="42">
-        <f>SUM(R70:T70)</f>
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="W70" s="28">
         <f>O70*V70</f>
-        <v>338892.32</v>
+        <v>322560.15999999997</v>
       </c>
       <c r="X70" s="28">
         <v>705</v>
@@ -7331,7 +7327,7 @@
       </c>
       <c r="AD70" s="28">
         <f t="shared" si="31"/>
-        <v>20925.580000000016</v>
+        <v>37257.740000000049</v>
       </c>
     </row>
     <row r="71" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -7386,12 +7382,11 @@
       </c>
       <c r="U71" s="28"/>
       <c r="V71" s="42">
-        <f>SUM(R71:T71)</f>
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="W71" s="28">
         <f>O71*V71</f>
-        <v>321416.50399999996</v>
+        <v>306894.674</v>
       </c>
       <c r="X71" s="28">
         <v>705</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AD71" s="28">
         <f t="shared" si="31"/>
-        <v>19846.501000000047</v>
+        <v>34368.331000000006</v>
       </c>
     </row>
     <row r="72" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -7467,12 +7462,11 @@
       </c>
       <c r="U72" s="28"/>
       <c r="V72" s="42">
-        <f>SUM(R72:T72)</f>
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="W72" s="28">
         <f>O72*V72</f>
-        <v>321783.696</v>
+        <v>307245.27600000001</v>
       </c>
       <c r="X72" s="28">
         <v>705</v>
@@ -7493,7 +7487,7 @@
       </c>
       <c r="AD72" s="28">
         <f t="shared" si="31"/>
-        <v>19869.173999999999</v>
+        <v>34407.593999999983</v>
       </c>
     </row>
     <row r="73" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -7548,12 +7542,11 @@
       </c>
       <c r="U73" s="28"/>
       <c r="V73" s="42">
-        <f>SUM(R73:T73)</f>
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="W73" s="28">
         <f>O73*V73</f>
-        <v>321291.67200000002</v>
+        <v>306775.48200000002</v>
       </c>
       <c r="X73" s="28">
         <v>705</v>
@@ -7574,7 +7567,7 @@
       </c>
       <c r="AD73" s="28">
         <f t="shared" si="31"/>
-        <v>19838.792999999947</v>
+        <v>34354.982999999949</v>
       </c>
       <c r="AE73" t="s">
         <v>130</v>
@@ -7632,12 +7625,11 @@
       </c>
       <c r="U74" s="28"/>
       <c r="V74" s="42">
-        <f>SUM(R74:T74)</f>
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="W74" s="28">
         <f>O74*V74</f>
-        <v>320101.78399999999</v>
+        <v>305639.35399999999</v>
       </c>
       <c r="X74" s="28">
         <v>705</v>
@@ -7658,7 +7650,7 @@
       </c>
       <c r="AD74" s="28">
         <f t="shared" ref="AD74" si="32">AC74-W74</f>
-        <v>19765.321000000054</v>
+        <v>34227.751000000047</v>
       </c>
       <c r="AE74" t="s">
         <v>131</v>
@@ -7716,12 +7708,11 @@
       </c>
       <c r="U75" s="28"/>
       <c r="V75" s="42">
-        <f>SUM(R75:T75)</f>
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="W75" s="28">
         <f>O75*V75</f>
-        <v>198109.712</v>
+        <v>189158.97200000001</v>
       </c>
       <c r="X75" s="28">
         <v>705</v>
@@ -7742,7 +7733,7 @@
       </c>
       <c r="AD75" s="28">
         <f t="shared" ref="AD75" si="33">AC75-W75</f>
-        <v>12232.678000000014</v>
+        <v>21183.418000000005</v>
       </c>
       <c r="AE75" t="s">
         <v>132</v>
@@ -7781,7 +7772,7 @@
       <c r="V76" s="24"/>
       <c r="W76" s="25">
         <f>+SUM(W67:W75)</f>
-        <v>2821172.656</v>
+        <v>2689678.5019999999</v>
       </c>
       <c r="X76" s="24"/>
       <c r="Y76" s="24"/>
@@ -7794,7 +7785,7 @@
       </c>
       <c r="AD76" s="25">
         <f>+SUM(AD67:AD75)</f>
-        <v>174198.91400000016</v>
+        <v>305693.06800000009</v>
       </c>
     </row>
     <row r="77" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -8504,8 +8495,7 @@
         <v>16</v>
       </c>
       <c r="R84" s="28">
-        <f>K84+30</f>
-        <v>30</v>
+        <v>668</v>
       </c>
       <c r="S84" s="28">
         <v>0</v>
@@ -8516,11 +8506,11 @@
       <c r="U84" s="28"/>
       <c r="V84" s="28">
         <f>R84+T84</f>
-        <v>10</v>
+        <v>648</v>
       </c>
       <c r="W84" s="28">
         <f>O84*V84</f>
-        <v>4982.58</v>
+        <v>322871.18400000001</v>
       </c>
       <c r="X84" s="28">
         <v>740</v>
@@ -8541,7 +8531,7 @@
       </c>
       <c r="AD84" s="28">
         <f>AC84-W84</f>
-        <v>363728.33999999997</v>
+        <v>45839.735999999975</v>
       </c>
       <c r="AE84" s="38" t="s">
         <v>134</v>
@@ -8594,8 +8584,7 @@
         <v>16</v>
       </c>
       <c r="R85" s="28">
-        <f>K85+30</f>
-        <v>30</v>
+        <v>668</v>
       </c>
       <c r="S85" s="28">
         <v>0</v>
@@ -8606,11 +8595,11 @@
       <c r="U85" s="28"/>
       <c r="V85" s="28">
         <f>R85+T85</f>
-        <v>10</v>
+        <v>648</v>
       </c>
       <c r="W85" s="28">
         <f>O85*V85</f>
-        <v>4994.8</v>
+        <v>323663.04000000004</v>
       </c>
       <c r="X85" s="28">
         <v>740</v>
@@ -8631,7 +8620,7 @@
       </c>
       <c r="AD85" s="28">
         <f t="shared" ref="AD85:AD86" si="38">AC85-W85</f>
-        <v>364620.4</v>
+        <v>45952.159999999974</v>
       </c>
       <c r="AE85" s="38" t="s">
         <v>135</v>
@@ -8684,8 +8673,7 @@
         <v>16</v>
       </c>
       <c r="R86" s="28">
-        <f>K86+30</f>
-        <v>30</v>
+        <v>668</v>
       </c>
       <c r="S86" s="28">
         <v>0</v>
@@ -8696,11 +8684,11 @@
       <c r="U86" s="28"/>
       <c r="V86" s="28">
         <f>R86+T86</f>
-        <v>10</v>
+        <v>648</v>
       </c>
       <c r="W86" s="28">
         <f>O86*V86</f>
-        <v>4984.92</v>
+        <v>323022.81599999999</v>
       </c>
       <c r="X86" s="28">
         <v>740</v>
@@ -8721,7 +8709,7 @@
       </c>
       <c r="AD86" s="28">
         <f t="shared" si="38"/>
-        <v>363899.16000000003</v>
+        <v>45861.264000000025</v>
       </c>
       <c r="AE86" s="38" t="s">
         <v>135</v>
@@ -8760,7 +8748,7 @@
       <c r="V87" s="24"/>
       <c r="W87" s="25">
         <f>+SUM(W84:W86)</f>
-        <v>14962.300000000001</v>
+        <v>969557.04</v>
       </c>
       <c r="X87" s="24"/>
       <c r="Y87" s="24"/>
@@ -8773,7 +8761,7 @@
       </c>
       <c r="AD87" s="25">
         <f>+SUM(AD84:AD86)</f>
-        <v>1092247.8999999999</v>
+        <v>137653.15999999997</v>
       </c>
     </row>
     <row r="88" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -8826,8 +8814,7 @@
         <v>16</v>
       </c>
       <c r="R88" s="28">
-        <f>K88+30</f>
-        <v>1032.0709999999999</v>
+        <v>675</v>
       </c>
       <c r="S88" s="28">
         <v>0</v>
@@ -8838,11 +8825,11 @@
       <c r="U88" s="28"/>
       <c r="V88" s="28">
         <f>R88+T88</f>
-        <v>1012.0709999999999</v>
+        <v>655</v>
       </c>
       <c r="W88" s="28">
         <f>O88*V88</f>
-        <v>505140.82923599996</v>
+        <v>326920.98</v>
       </c>
       <c r="X88" s="28">
         <v>740</v>
@@ -8863,7 +8850,7 @@
       </c>
       <c r="AD88" s="28">
         <f t="shared" ref="AD88:AD90" si="39">AC88-W88</f>
-        <v>-135794.98923599999</v>
+        <v>42424.859999999986</v>
       </c>
       <c r="AE88" s="38" t="s">
         <v>175</v>
@@ -8916,8 +8903,7 @@
         <v>16</v>
       </c>
       <c r="R89" s="28">
-        <f>K89+30</f>
-        <v>30</v>
+        <v>675</v>
       </c>
       <c r="S89" s="28">
         <v>0</v>
@@ -8928,11 +8914,11 @@
       <c r="U89" s="28"/>
       <c r="V89" s="28">
         <f>R89+T89</f>
-        <v>10</v>
+        <v>655</v>
       </c>
       <c r="W89" s="28">
         <f>O89*V89</f>
-        <v>4982.7</v>
+        <v>326366.84999999998</v>
       </c>
       <c r="X89" s="28">
         <v>740</v>
@@ -8953,7 +8939,7 @@
       </c>
       <c r="AD89" s="28">
         <f t="shared" si="39"/>
-        <v>363737.1</v>
+        <v>42352.950000000012</v>
       </c>
       <c r="AE89" s="38" t="s">
         <v>185</v>
@@ -9006,8 +8992,7 @@
         <v>16</v>
       </c>
       <c r="R90" s="28">
-        <f>K90+30</f>
-        <v>30</v>
+        <v>675</v>
       </c>
       <c r="S90" s="28">
         <v>0</v>
@@ -9018,11 +9003,11 @@
       <c r="U90" s="28"/>
       <c r="V90" s="28">
         <f>R90+T90</f>
-        <v>10</v>
+        <v>655</v>
       </c>
       <c r="W90" s="28">
         <f>O90*V90</f>
-        <v>4996.18</v>
+        <v>327249.78999999998</v>
       </c>
       <c r="X90" s="28">
         <v>740</v>
@@ -9043,7 +9028,7 @@
       </c>
       <c r="AD90" s="28">
         <f t="shared" si="39"/>
-        <v>364721.14</v>
+        <v>42467.530000000028</v>
       </c>
       <c r="AE90" s="38" t="s">
         <v>196</v>
@@ -9079,7 +9064,7 @@
       <c r="V91" s="24"/>
       <c r="W91" s="25">
         <f>+SUM(W88:W90)</f>
-        <v>515119.70923599997</v>
+        <v>980537.61999999988</v>
       </c>
       <c r="X91" s="24"/>
       <c r="Y91" s="24"/>
@@ -9092,7 +9077,7 @@
       </c>
       <c r="AD91" s="25">
         <f>+SUM(AD88:AD90)</f>
-        <v>592663.250764</v>
+        <v>127245.34000000003</v>
       </c>
     </row>
     <row r="92" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -9801,11 +9786,10 @@
         <v>16</v>
       </c>
       <c r="R99" s="42">
-        <f>K99</f>
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="S99" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="28">
         <v>-30</v>
@@ -9813,11 +9797,11 @@
       <c r="U99" s="28"/>
       <c r="V99" s="28">
         <f>R99+T99</f>
-        <v>-30</v>
+        <v>586</v>
       </c>
       <c r="W99" s="28">
         <f>O99*V99</f>
-        <v>-15060.480000000001</v>
+        <v>294181.37599999999</v>
       </c>
       <c r="X99" s="28">
         <v>710</v>
@@ -9838,7 +9822,7 @@
       </c>
       <c r="AD99" s="28">
         <f t="shared" ref="AD99:AD100" si="42">AC99-W99</f>
-        <v>371491.83999999997</v>
+        <v>62249.983999999997</v>
       </c>
       <c r="AE99" s="38" t="s">
         <v>215</v>
@@ -9886,8 +9870,7 @@
         <v>16</v>
       </c>
       <c r="R100" s="42">
-        <f>K100</f>
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="S100" s="28">
         <v>0</v>
@@ -9898,11 +9881,11 @@
       <c r="U100" s="28"/>
       <c r="V100" s="28">
         <f>R100+T100</f>
-        <v>-30</v>
+        <v>586</v>
       </c>
       <c r="W100" s="28">
         <f>O100*V100</f>
-        <v>-15001.65</v>
+        <v>293032.23</v>
       </c>
       <c r="X100" s="28">
         <v>710</v>
@@ -9923,7 +9906,7 @@
       </c>
       <c r="AD100" s="28">
         <f t="shared" si="42"/>
-        <v>370040.7</v>
+        <v>62006.820000000007</v>
       </c>
       <c r="AE100" s="38" t="s">
         <v>215</v>
@@ -9960,7 +9943,7 @@
       <c r="V101" s="24"/>
       <c r="W101" s="25">
         <f>+SUM(W99:W100)</f>
-        <v>-30062.13</v>
+        <v>587213.60599999991</v>
       </c>
       <c r="X101" s="24"/>
       <c r="Y101" s="24"/>
@@ -9973,7 +9956,7 @@
       </c>
       <c r="AD101" s="25">
         <f>+SUM(AD99:AD100)</f>
-        <v>741532.54</v>
+        <v>124256.804</v>
       </c>
     </row>
     <row r="102" spans="1:44" ht="32" x14ac:dyDescent="0.2">
@@ -18124,7 +18107,7 @@
       </c>
       <c r="AD202" s="17">
         <f>SUM(AD122,AD101,AD91,AD87,AD76,AD66,AD149,)</f>
-        <v>3134788.9567640005</v>
+        <v>1228994.7240000002</v>
       </c>
     </row>
     <row r="203" spans="1:31" x14ac:dyDescent="0.2">
@@ -18624,7 +18607,7 @@
       <c r="Y241" s="68"/>
       <c r="Z241" s="69">
         <f>X84-R84</f>
-        <v>710</v>
+        <v>72</v>
       </c>
       <c r="AA241" s="69"/>
       <c r="AB241" s="70">
@@ -18693,7 +18676,7 @@
       </c>
       <c r="Z243" s="69">
         <f>Z241*Z242</f>
-        <v>1062323.3</v>
+        <v>107728.56</v>
       </c>
       <c r="AA243" s="69"/>
       <c r="AB243" s="70">
@@ -18760,7 +18743,7 @@
       </c>
       <c r="Z245" s="92">
         <f>Z243*Z244</f>
-        <v>382436.38799999998</v>
+        <v>38782.281599999995</v>
       </c>
       <c r="AA245" s="92"/>
       <c r="AB245" s="93">
@@ -18862,7 +18845,7 @@
       <c r="AA249" s="95"/>
       <c r="AB249" s="93">
         <f>AB245+Z245</f>
-        <v>421238.73167999997</v>
+        <v>77584.625279999993</v>
       </c>
       <c r="AC249" s="68" t="s">
         <v>308</v>
@@ -18895,7 +18878,7 @@
       </c>
       <c r="AD250" s="70">
         <f>AB260</f>
-        <v>-332197.73167999997</v>
+        <v>11456.374720000007</v>
       </c>
       <c r="AF250" s="80">
         <v>325000</v>
@@ -18952,7 +18935,7 @@
       </c>
       <c r="AD252" s="100">
         <f>AD249-AD250</f>
-        <v>410896.92343999993</v>
+        <v>67242.81703999998</v>
       </c>
       <c r="AF252" s="80">
         <v>514200</v>
@@ -19013,7 +18996,7 @@
       </c>
       <c r="AD254" s="100">
         <f>AD252-AD253</f>
-        <v>360896.92343999993</v>
+        <v>17242.81703999998</v>
       </c>
       <c r="AF254" s="80">
         <v>632000</v>
@@ -19114,7 +19097,7 @@
       <c r="AA258" s="95"/>
       <c r="AB258" s="93">
         <f>AB249-AB251+AB252-AB253-AB254+AB255+AB256-AB257</f>
-        <v>397197.73167999997</v>
+        <v>53543.625279999993</v>
       </c>
       <c r="AC258" s="68"/>
       <c r="AD258" s="72"/>
@@ -19163,7 +19146,7 @@
       <c r="AA260" s="75"/>
       <c r="AB260" s="102">
         <f>AB259-AB258</f>
-        <v>-332197.73167999997</v>
+        <v>11456.374720000007</v>
       </c>
       <c r="AC260" s="68"/>
       <c r="AD260" s="72"/>
@@ -19391,7 +19374,7 @@
       </c>
       <c r="AE270" s="53">
         <f>SUM(W66,W76,W87,W91,W101,W122)</f>
-        <v>6665813.6082359999</v>
+        <v>8571607.8409999982</v>
       </c>
       <c r="AF270" s="86">
         <f>SUMIF(AJ220:AJ265,"Arauco",AF220:AF265)</f>
@@ -19402,7 +19385,7 @@
       </c>
       <c r="AH270" s="87">
         <f>AE270-AF270</f>
-        <v>-1923415.3917640001</v>
+        <v>-17621.159000001848</v>
       </c>
     </row>
     <row r="271" spans="18:36" x14ac:dyDescent="0.2">
@@ -19451,7 +19434,7 @@
       </c>
       <c r="AE272" s="53">
         <f>SUM(AE270:AE271)</f>
-        <v>11061999.943236001</v>
+        <v>12967794.175999999</v>
       </c>
       <c r="AF272" s="86">
         <f>SUM(AF225:AF265)</f>
@@ -19462,7 +19445,7 @@
       </c>
       <c r="AH272" s="87">
         <f>SUM(AH270:AH271)</f>
-        <v>-1853230.0567640001</v>
+        <v>52564.175999998115</v>
       </c>
     </row>
     <row r="273" spans="24:40" x14ac:dyDescent="0.2">
@@ -20016,7 +19999,7 @@
       </c>
       <c r="AN305" s="17">
         <f>W76</f>
-        <v>2821172.656</v>
+        <v>2689678.5019999999</v>
       </c>
     </row>
     <row r="306" spans="32:40" x14ac:dyDescent="0.2">
@@ -20025,7 +20008,7 @@
       </c>
       <c r="AN306" s="45">
         <f>AN304-AN305</f>
-        <v>-103172.65599999996</v>
+        <v>28321.498000000138</v>
       </c>
     </row>
     <row r="307" spans="32:40" x14ac:dyDescent="0.2">
@@ -20096,7 +20079,7 @@
       </c>
       <c r="AN313" s="17">
         <f>W67+W68+W69+W70+W71+W72+W73+(O74*668)+(O75*668)</f>
-        <v>2824294.412</v>
+        <v>2716213.4279999998</v>
       </c>
     </row>
     <row r="314" spans="32:40" x14ac:dyDescent="0.2">
@@ -20105,7 +20088,7 @@
       </c>
       <c r="AN314" s="45">
         <f>AN312-AN313</f>
-        <v>-106294.41200000001</v>
+        <v>1786.5720000001602</v>
       </c>
     </row>
     <row r="316" spans="32:40" x14ac:dyDescent="0.2">
@@ -20131,11 +20114,11 @@
       </c>
       <c r="AG318" s="17">
         <f>X67-V67</f>
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AH318" s="17">
         <f>AF318*AG318</f>
-        <v>457.56000000000103</v>
+        <v>814.68000000000188</v>
       </c>
     </row>
     <row r="319" spans="32:40" x14ac:dyDescent="0.2">
@@ -20145,11 +20128,11 @@
       </c>
       <c r="AG319" s="17">
         <f>X68-V68</f>
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AH319" s="17">
         <f t="shared" ref="AH319:AH326" si="92">AF319*AG319</f>
-        <v>376.95400000000069</v>
+        <v>671.16200000000117</v>
       </c>
     </row>
     <row r="320" spans="32:40" x14ac:dyDescent="0.2">
@@ -20159,11 +20142,11 @@
       </c>
       <c r="AG320" s="17">
         <f>X69-V69</f>
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AH320" s="17">
         <f t="shared" si="92"/>
-        <v>-613.64699999999937</v>
+        <v>-1092.590999999999</v>
       </c>
     </row>
     <row r="321" spans="32:38" x14ac:dyDescent="0.2">
@@ -20173,11 +20156,11 @@
       </c>
       <c r="AG321" s="17">
         <f>X70-V70</f>
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AH321" s="17">
         <f t="shared" si="92"/>
-        <v>425.57999999999981</v>
+        <v>757.73999999999967</v>
       </c>
     </row>
     <row r="322" spans="32:38" x14ac:dyDescent="0.2">
@@ -20187,11 +20170,11 @@
       </c>
       <c r="AG322" s="17">
         <f>X71-V71</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AH322" s="17">
         <f t="shared" si="92"/>
-        <v>-653.49900000000093</v>
+        <v>-1131.6690000000015</v>
       </c>
     </row>
     <row r="323" spans="32:38" x14ac:dyDescent="0.2">
@@ -20201,11 +20184,11 @@
       </c>
       <c r="AG323" s="17">
         <f>X72-V72</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AH323" s="17">
         <f t="shared" si="92"/>
-        <v>-630.82600000000093</v>
+        <v>-1092.4060000000018</v>
       </c>
     </row>
     <row r="324" spans="32:38" x14ac:dyDescent="0.2">
@@ -20215,11 +20198,11 @@
       </c>
       <c r="AG324" s="17">
         <f>X73-V73</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AH324" s="17">
         <f t="shared" si="92"/>
-        <v>-661.20700000000033</v>
+        <v>-1145.0170000000007</v>
       </c>
     </row>
     <row r="325" spans="32:38" x14ac:dyDescent="0.2">
@@ -20229,11 +20212,11 @@
       </c>
       <c r="AG325" s="17">
         <f>X74-V74</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AH325" s="17">
         <f t="shared" si="92"/>
-        <v>-734.67899999999929</v>
+        <v>-1272.2489999999989</v>
       </c>
     </row>
     <row r="326" spans="32:38" x14ac:dyDescent="0.2">
@@ -20243,11 +20226,11 @@
       </c>
       <c r="AG326" s="17">
         <f>X75-V75</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AH326" s="17">
         <f t="shared" si="92"/>
-        <v>-67.321999999999832</v>
+        <v>-116.58199999999971</v>
       </c>
     </row>
     <row r="327" spans="32:38" x14ac:dyDescent="0.2">
@@ -20265,7 +20248,7 @@
       </c>
       <c r="AH328" s="47">
         <f>SUM(AH318:AH326)</f>
-        <v>-2101.0859999999989</v>
+        <v>-3606.9319999999993</v>
       </c>
     </row>
     <row r="329" spans="32:38" x14ac:dyDescent="0.2">

--- a/Sales_Report.xlsx
+++ b/Sales_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardobazua/bza-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1C2C7B-5645-834D-B675-B9049519E079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6C31B1-2EB2-F840-B376-18D78FA809B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="30240" windowHeight="17480" xr2:uid="{A69E99B4-FD75-534F-A443-AF5D6F49D11E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="421">
   <si>
     <t>ORDEN DE COMPRA</t>
   </si>
@@ -971,6 +971,9 @@
     <t>Utilidad PVR</t>
   </si>
   <si>
+    <t>precio</t>
+  </si>
+  <si>
     <t>Precio</t>
   </si>
   <si>
@@ -1076,9 +1079,6 @@
     <t>pagado 19/dic</t>
   </si>
   <si>
-    <t>]</t>
-  </si>
-  <si>
     <t>surcharge logistico</t>
   </si>
   <si>
@@ -1157,9 +1157,6 @@
     <t>IX0041-2</t>
   </si>
   <si>
-    <t>Utilidades 2025</t>
-  </si>
-  <si>
     <t>Utilidades 2026</t>
   </si>
   <si>
@@ -1230,6 +1227,81 @@
   </si>
   <si>
     <t>IX0042-9</t>
+  </si>
+  <si>
+    <t>X0043</t>
+  </si>
+  <si>
+    <t>IX0043-1</t>
+  </si>
+  <si>
+    <t>IX0043-2</t>
+  </si>
+  <si>
+    <t>IX0043-3</t>
+  </si>
+  <si>
+    <t>IX0043-4</t>
+  </si>
+  <si>
+    <t>IX0043-5</t>
+  </si>
+  <si>
+    <t>IX0043-6</t>
+  </si>
+  <si>
+    <t>IX0043-7</t>
+  </si>
+  <si>
+    <t>IX0043-8</t>
+  </si>
+  <si>
+    <t>IX0043-9</t>
+  </si>
+  <si>
+    <t>proteina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ostion </t>
+  </si>
+  <si>
+    <t>unidad</t>
+  </si>
+  <si>
+    <t>piezas</t>
+  </si>
+  <si>
+    <t>camaron</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>pescado blanco</t>
+  </si>
+  <si>
+    <t>atun</t>
+  </si>
+  <si>
+    <t>callo</t>
+  </si>
+  <si>
+    <t>03/20/26</t>
+  </si>
+  <si>
+    <t>IX0043-10</t>
+  </si>
+  <si>
+    <t>IX0043-11</t>
+  </si>
+  <si>
+    <t>IX0043-12</t>
+  </si>
+  <si>
+    <t>540 extra</t>
+  </si>
+  <si>
+    <t>bajo</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1710,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1851,9 +1923,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1878,9 +1947,6 @@
     <xf numFmtId="181" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2219,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E60E4A7-44BB-EF45-AA03-B01A671D9B12}">
-  <dimension ref="A3:AR339"/>
+  <dimension ref="A3:AR342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -2255,6 +2321,7 @@
     <col min="39" max="39" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2287,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
@@ -2309,7 +2376,7 @@
         <v>59</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>60</v>
@@ -2327,7 +2394,7 @@
         <v>59</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>58</v>
@@ -6274,27 +6341,27 @@
       <c r="I58" s="39"/>
       <c r="J58" s="39"/>
       <c r="K58" s="39"/>
-      <c r="L58" s="118">
+      <c r="L58" s="117">
         <v>2025</v>
       </c>
-      <c r="M58" s="119"/>
-      <c r="N58" s="119"/>
-      <c r="O58" s="119"/>
-      <c r="P58" s="119"/>
-      <c r="Q58" s="119"/>
-      <c r="R58" s="119"/>
-      <c r="S58" s="119"/>
-      <c r="T58" s="119"/>
-      <c r="U58" s="119"/>
-      <c r="V58" s="119"/>
-      <c r="W58" s="119"/>
-      <c r="X58" s="119"/>
-      <c r="Y58" s="119"/>
-      <c r="Z58" s="119"/>
-      <c r="AA58" s="119"/>
-      <c r="AB58" s="119"/>
-      <c r="AC58" s="119"/>
-      <c r="AD58" s="120"/>
+      <c r="M58" s="118"/>
+      <c r="N58" s="118"/>
+      <c r="O58" s="118"/>
+      <c r="P58" s="118"/>
+      <c r="Q58" s="118"/>
+      <c r="R58" s="118"/>
+      <c r="S58" s="118"/>
+      <c r="T58" s="118"/>
+      <c r="U58" s="118"/>
+      <c r="V58" s="118"/>
+      <c r="W58" s="118"/>
+      <c r="X58" s="118"/>
+      <c r="Y58" s="118"/>
+      <c r="Z58" s="118"/>
+      <c r="AA58" s="118"/>
+      <c r="AB58" s="118"/>
+      <c r="AC58" s="118"/>
+      <c r="AD58" s="119"/>
       <c r="AF58" s="3"/>
       <c r="AG58" s="3"/>
       <c r="AH58" s="3"/>
@@ -6332,10 +6399,10 @@
       <c r="J59" s="11"/>
       <c r="K59" s="37"/>
       <c r="L59" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M59" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M59" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N59" s="27"/>
       <c r="O59" s="27">
@@ -6427,10 +6494,10 @@
       <c r="J60" s="11"/>
       <c r="K60" s="37"/>
       <c r="L60" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M60" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M60" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N60" s="27"/>
       <c r="O60" s="27">
@@ -6520,10 +6587,10 @@
       <c r="J61" s="11"/>
       <c r="K61" s="37"/>
       <c r="L61" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M61" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M61" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N61" s="27"/>
       <c r="O61" s="27">
@@ -6614,10 +6681,10 @@
       <c r="J62" s="11"/>
       <c r="K62" s="37"/>
       <c r="L62" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M62" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M62" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N62" s="27"/>
       <c r="O62" s="27">
@@ -6706,10 +6773,10 @@
       <c r="J63" s="11"/>
       <c r="K63" s="37"/>
       <c r="L63" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M63" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M63" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N63" s="27"/>
       <c r="O63" s="27">
@@ -6799,10 +6866,10 @@
       <c r="J64" s="11"/>
       <c r="K64" s="37"/>
       <c r="L64" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M64" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M64" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N64" s="27"/>
       <c r="O64" s="27">
@@ -6891,10 +6958,10 @@
       <c r="J65" s="11"/>
       <c r="K65" s="37"/>
       <c r="L65" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M65" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M65" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N65" s="27"/>
       <c r="O65" s="27">
@@ -7031,10 +7098,10 @@
         <v>634</v>
       </c>
       <c r="L67" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M67" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M67" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N67" s="27"/>
       <c r="O67" s="27">
@@ -7114,10 +7181,10 @@
         <v>634</v>
       </c>
       <c r="L68" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M68" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M68" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N68" s="27"/>
       <c r="O68" s="27">
@@ -7195,10 +7262,10 @@
         <v>634</v>
       </c>
       <c r="L69" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M69" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M69" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N69" s="27"/>
       <c r="O69" s="27">
@@ -7275,10 +7342,10 @@
         <v>634</v>
       </c>
       <c r="L70" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M70" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M70" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N70" s="27"/>
       <c r="O70" s="27">
@@ -7355,10 +7422,10 @@
         <v>634</v>
       </c>
       <c r="L71" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M71" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M71" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N71" s="27"/>
       <c r="O71" s="27">
@@ -7435,10 +7502,10 @@
         <v>634</v>
       </c>
       <c r="L72" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M72" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M72" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N72" s="27"/>
       <c r="O72" s="27">
@@ -7515,10 +7582,10 @@
         <v>634</v>
       </c>
       <c r="L73" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M73" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M73" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N73" s="27"/>
       <c r="O73" s="27">
@@ -7598,10 +7665,10 @@
         <v>634</v>
       </c>
       <c r="L74" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M74" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M74" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N74" s="27"/>
       <c r="O74" s="27">
@@ -7681,10 +7748,10 @@
         <v>634</v>
       </c>
       <c r="L75" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M75" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M75" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N75" s="27"/>
       <c r="O75" s="27">
@@ -7742,7 +7809,7 @@
     <row r="76" spans="1:44" ht="20" x14ac:dyDescent="0.25">
       <c r="A76" s="61">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="7"/>
@@ -7815,14 +7882,14 @@
       </c>
       <c r="J77" s="62">
         <f ca="1">I77-$A$76</f>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K77" s="37"/>
       <c r="L77" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M77" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N77" s="27" t="s">
         <v>122</v>
@@ -7918,14 +7985,14 @@
       </c>
       <c r="J78" s="62">
         <f t="shared" ref="J78:J97" ca="1" si="35">I78-$A$76</f>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K78" s="37"/>
       <c r="L78" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M78" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N78" s="27" t="s">
         <v>124</v>
@@ -8021,14 +8088,14 @@
       </c>
       <c r="J79" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K79" s="37"/>
       <c r="L79" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M79" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N79" s="27" t="s">
         <v>125</v>
@@ -8124,14 +8191,14 @@
       </c>
       <c r="J80" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K80" s="37"/>
       <c r="L80" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M80" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N80" s="27" t="s">
         <v>126</v>
@@ -8227,14 +8294,14 @@
       </c>
       <c r="J81" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K81" s="37"/>
       <c r="L81" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M81" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N81" s="27" t="s">
         <v>121</v>
@@ -8330,14 +8397,14 @@
       </c>
       <c r="J82" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-284</v>
+        <v>-300</v>
       </c>
       <c r="K82" s="37"/>
       <c r="L82" s="27" t="s">
         <v>118</v>
       </c>
       <c r="M82" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N82" s="27" t="s">
         <v>120</v>
@@ -8475,14 +8542,14 @@
       </c>
       <c r="J84" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-264</v>
+        <v>-280</v>
       </c>
       <c r="K84" s="37"/>
       <c r="L84" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M84" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M84" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N84" s="27"/>
       <c r="O84" s="27">
@@ -8564,14 +8631,14 @@
       </c>
       <c r="J85" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-256</v>
+        <v>-272</v>
       </c>
       <c r="K85" s="37"/>
       <c r="L85" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M85" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M85" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N85" s="27"/>
       <c r="O85" s="27">
@@ -8653,14 +8720,14 @@
       </c>
       <c r="J86" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-253</v>
+        <v>-269</v>
       </c>
       <c r="K86" s="37"/>
       <c r="L86" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M86" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M86" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N86" s="27"/>
       <c r="O86" s="27">
@@ -8791,17 +8858,17 @@
       </c>
       <c r="J88" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-238</v>
+        <v>-254</v>
       </c>
       <c r="K88" s="37">
         <f>O101</f>
         <v>1002.071</v>
       </c>
       <c r="L88" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M88" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M88" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N88" s="27"/>
       <c r="O88" s="27">
@@ -8883,14 +8950,14 @@
       </c>
       <c r="J89" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-238</v>
+        <v>-254</v>
       </c>
       <c r="K89" s="37"/>
       <c r="L89" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M89" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M89" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N89" s="27"/>
       <c r="O89" s="27">
@@ -8972,14 +9039,14 @@
       </c>
       <c r="J90" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-230</v>
+        <v>-246</v>
       </c>
       <c r="K90" s="37"/>
       <c r="L90" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M90" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M90" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N90" s="27"/>
       <c r="O90" s="27">
@@ -9107,14 +9174,14 @@
       </c>
       <c r="J92" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-245</v>
+        <v>-261</v>
       </c>
       <c r="K92" s="37"/>
       <c r="L92" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M92" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N92" s="27" t="s">
         <v>176</v>
@@ -9211,14 +9278,14 @@
       </c>
       <c r="J93" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-245</v>
+        <v>-261</v>
       </c>
       <c r="K93" s="37"/>
       <c r="L93" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M93" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N93" s="27" t="s">
         <v>177</v>
@@ -9314,14 +9381,14 @@
       </c>
       <c r="J94" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-245</v>
+        <v>-261</v>
       </c>
       <c r="K94" s="37"/>
       <c r="L94" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M94" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N94" s="27" t="s">
         <v>178</v>
@@ -9417,14 +9484,14 @@
       </c>
       <c r="J95" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-245</v>
+        <v>-261</v>
       </c>
       <c r="K95" s="37"/>
       <c r="L95" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M95" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N95" s="27" t="s">
         <v>179</v>
@@ -9520,14 +9587,14 @@
       </c>
       <c r="J96" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-244</v>
+        <v>-260</v>
       </c>
       <c r="K96" s="37"/>
       <c r="L96" s="27" t="s">
         <v>119</v>
       </c>
       <c r="M96" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N96" s="27" t="s">
         <v>180</v>
@@ -9623,14 +9690,14 @@
       </c>
       <c r="J97" s="62">
         <f t="shared" ca="1" si="35"/>
-        <v>-238</v>
+        <v>-254</v>
       </c>
       <c r="K97" s="37"/>
       <c r="L97" s="27" t="s">
         <v>123</v>
       </c>
       <c r="M97" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N97" s="27" t="s">
         <v>184</v>
@@ -9770,10 +9837,10 @@
       <c r="J99" s="62"/>
       <c r="K99" s="37"/>
       <c r="L99" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M99" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M99" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N99" s="27"/>
       <c r="O99" s="27">
@@ -9854,10 +9921,10 @@
       <c r="J100" s="62"/>
       <c r="K100" s="37"/>
       <c r="L100" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M100" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M100" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N100" s="27"/>
       <c r="O100" s="27">
@@ -9990,7 +10057,7 @@
         <v>123</v>
       </c>
       <c r="M102" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N102" s="27"/>
       <c r="O102" s="27">
@@ -10090,7 +10157,7 @@
         <v>123</v>
       </c>
       <c r="M103" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N103" s="27"/>
       <c r="O103" s="27">
@@ -10189,7 +10256,7 @@
         <v>119</v>
       </c>
       <c r="M104" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N104" s="27"/>
       <c r="O104" s="27">
@@ -10288,7 +10355,7 @@
         <v>119</v>
       </c>
       <c r="M105" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N105" s="27"/>
       <c r="O105" s="27">
@@ -10387,7 +10454,7 @@
         <v>119</v>
       </c>
       <c r="M106" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N106" s="27"/>
       <c r="O106" s="63">
@@ -10486,7 +10553,7 @@
         <v>199</v>
       </c>
       <c r="M107" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N107" s="27"/>
       <c r="O107" s="63">
@@ -10585,7 +10652,7 @@
         <v>118</v>
       </c>
       <c r="M108" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N108" s="27"/>
       <c r="O108" s="27">
@@ -10730,7 +10797,7 @@
         <v>123</v>
       </c>
       <c r="M110" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N110" s="27"/>
       <c r="O110" s="27">
@@ -10828,7 +10895,7 @@
         <v>123</v>
       </c>
       <c r="M111" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N111" s="27"/>
       <c r="O111" s="27">
@@ -10926,7 +10993,7 @@
         <v>119</v>
       </c>
       <c r="M112" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N112" s="27"/>
       <c r="O112" s="27">
@@ -11024,7 +11091,7 @@
         <v>119</v>
       </c>
       <c r="M113" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N113" s="27"/>
       <c r="O113" s="27">
@@ -11122,7 +11189,7 @@
         <v>199</v>
       </c>
       <c r="M114" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N114" s="27"/>
       <c r="O114" s="27">
@@ -11220,7 +11287,7 @@
         <v>118</v>
       </c>
       <c r="M115" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N115" s="27"/>
       <c r="O115" s="27">
@@ -11364,7 +11431,7 @@
         <v>227</v>
       </c>
       <c r="M117" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N117" s="27"/>
       <c r="O117" s="27">
@@ -11506,10 +11573,10 @@
       <c r="J119" s="11"/>
       <c r="K119" s="37"/>
       <c r="L119" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M119" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M119" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N119" s="27"/>
       <c r="O119" s="27">
@@ -11605,10 +11672,10 @@
       <c r="J120" s="11"/>
       <c r="K120" s="37"/>
       <c r="L120" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M120" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M120" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N120" s="27"/>
       <c r="O120" s="27">
@@ -11705,10 +11772,10 @@
       <c r="J121" s="11"/>
       <c r="K121" s="37"/>
       <c r="L121" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="M121" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="M121" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="N121" s="27"/>
       <c r="O121" s="27">
@@ -11857,7 +11924,7 @@
         <v>239</v>
       </c>
       <c r="M123" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N123" s="27"/>
       <c r="O123" s="27">
@@ -11956,7 +12023,7 @@
         <v>239</v>
       </c>
       <c r="M124" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N124" s="27"/>
       <c r="O124" s="27">
@@ -12055,7 +12122,7 @@
         <v>118</v>
       </c>
       <c r="M125" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N125" s="27"/>
       <c r="O125" s="27">
@@ -12154,7 +12221,7 @@
         <v>246</v>
       </c>
       <c r="M126" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N126" s="27"/>
       <c r="O126" s="27">
@@ -12253,7 +12320,7 @@
         <v>119</v>
       </c>
       <c r="M127" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N127" s="27"/>
       <c r="O127" s="27">
@@ -12352,7 +12419,7 @@
         <v>239</v>
       </c>
       <c r="M128" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N128" s="27"/>
       <c r="O128" s="27">
@@ -12451,7 +12518,7 @@
         <v>246</v>
       </c>
       <c r="M129" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N129" s="27"/>
       <c r="O129" s="27">
@@ -12550,7 +12617,7 @@
         <v>241</v>
       </c>
       <c r="M130" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N130" s="27"/>
       <c r="O130" s="27">
@@ -12695,7 +12762,7 @@
         <v>239</v>
       </c>
       <c r="M132" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N132" s="27"/>
       <c r="O132" s="27">
@@ -12794,7 +12861,7 @@
         <v>119</v>
       </c>
       <c r="M133" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N133" s="27"/>
       <c r="O133" s="27">
@@ -12893,7 +12960,7 @@
         <v>239</v>
       </c>
       <c r="M134" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N134" s="27"/>
       <c r="O134" s="27">
@@ -12992,7 +13059,7 @@
         <v>119</v>
       </c>
       <c r="M135" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N135" s="27"/>
       <c r="O135" s="27">
@@ -13091,7 +13158,7 @@
         <v>239</v>
       </c>
       <c r="M136" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N136" s="27"/>
       <c r="O136" s="27">
@@ -13190,7 +13257,7 @@
         <v>119</v>
       </c>
       <c r="M137" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N137" s="27"/>
       <c r="O137" s="27">
@@ -13289,7 +13356,7 @@
         <v>241</v>
       </c>
       <c r="M138" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N138" s="27"/>
       <c r="O138" s="27">
@@ -13388,7 +13455,7 @@
         <v>241</v>
       </c>
       <c r="M139" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N139" s="27"/>
       <c r="O139" s="27">
@@ -13487,7 +13554,7 @@
         <v>123</v>
       </c>
       <c r="M140" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N140" s="27"/>
       <c r="O140" s="27">
@@ -13586,7 +13653,7 @@
         <v>119</v>
       </c>
       <c r="M141" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N141" s="27"/>
       <c r="O141" s="27">
@@ -13685,7 +13752,7 @@
         <v>242</v>
       </c>
       <c r="M142" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N142" s="27"/>
       <c r="O142" s="27">
@@ -13830,7 +13897,7 @@
         <v>227</v>
       </c>
       <c r="M144" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N144" s="27"/>
       <c r="O144" s="27">
@@ -13927,7 +13994,7 @@
         <v>227</v>
       </c>
       <c r="M145" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N145" s="27"/>
       <c r="O145" s="27">
@@ -14269,7 +14336,7 @@
         <v>227</v>
       </c>
       <c r="M150" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N150" s="27"/>
       <c r="O150" s="27">
@@ -14321,7 +14388,7 @@
         <v>17264.920000000006</v>
       </c>
       <c r="AE150" s="38" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF150" s="3"/>
       <c r="AI150" s="3"/>
@@ -14364,7 +14431,7 @@
         <v>227</v>
       </c>
       <c r="M151" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N151" s="27"/>
       <c r="O151" s="27">
@@ -14416,7 +14483,7 @@
         <v>17702.68</v>
       </c>
       <c r="AE151" s="38" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF151" s="3"/>
       <c r="AI151" s="3"/>
@@ -14459,7 +14526,7 @@
         <v>227</v>
       </c>
       <c r="M152" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N152" s="27"/>
       <c r="O152" s="27">
@@ -14511,7 +14578,7 @@
         <v>17788.18</v>
       </c>
       <c r="AE152" s="38" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF152" s="14"/>
       <c r="AI152" s="3"/>
@@ -14601,7 +14668,7 @@
         <v>239</v>
       </c>
       <c r="M154" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N154" s="27"/>
       <c r="O154" s="27">
@@ -14653,7 +14720,7 @@
         <v>17006.519999999997</v>
       </c>
       <c r="AE154" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF154" s="3"/>
       <c r="AG154" s="14"/>
@@ -14697,7 +14764,7 @@
         <v>239</v>
       </c>
       <c r="M155" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N155" s="27"/>
       <c r="O155" s="27">
@@ -14749,7 +14816,7 @@
         <v>17389.180000000008</v>
       </c>
       <c r="AE155" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF155" s="3"/>
       <c r="AG155" s="14"/>
@@ -14793,7 +14860,7 @@
         <v>119</v>
       </c>
       <c r="M156" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N156" s="27"/>
       <c r="O156" s="27">
@@ -14845,7 +14912,7 @@
         <v>17209.82</v>
       </c>
       <c r="AE156" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF156" s="3"/>
       <c r="AG156" s="14"/>
@@ -14889,7 +14956,7 @@
         <v>119</v>
       </c>
       <c r="M157" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N157" s="27"/>
       <c r="O157" s="27">
@@ -14941,7 +15008,7 @@
         <v>17604.260000000009</v>
       </c>
       <c r="AE157" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF157" s="3"/>
       <c r="AG157" s="14"/>
@@ -14985,7 +15052,7 @@
         <v>242</v>
       </c>
       <c r="M158" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N158" s="27"/>
       <c r="O158" s="27">
@@ -15037,7 +15104,7 @@
         <v>17632.379999999997</v>
       </c>
       <c r="AE158" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF158" s="3"/>
       <c r="AG158" s="14"/>
@@ -15081,7 +15148,7 @@
         <v>242</v>
       </c>
       <c r="M159" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N159" s="27"/>
       <c r="O159" s="27">
@@ -15133,7 +15200,7 @@
         <v>17682.729999999996</v>
       </c>
       <c r="AE159" s="38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF159" s="3"/>
       <c r="AG159" s="14"/>
@@ -15175,7 +15242,7 @@
       <c r="K160" s="3"/>
       <c r="L160" s="27"/>
       <c r="M160" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N160" s="27"/>
       <c r="O160" s="27">
@@ -15227,7 +15294,7 @@
         <v>17216.659999999996</v>
       </c>
       <c r="AE160" s="38" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AF160" s="3"/>
       <c r="AG160" s="14"/>
@@ -15291,11 +15358,11 @@
     <row r="162" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>12</v>
@@ -15316,7 +15383,7 @@
         <v>241</v>
       </c>
       <c r="M162" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N162" s="27"/>
       <c r="O162" s="27">
@@ -15368,7 +15435,7 @@
         <v>14804.294999999998</v>
       </c>
       <c r="AE162" s="38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF162" s="3"/>
       <c r="AG162" s="14"/>
@@ -15386,11 +15453,11 @@
     <row r="163" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>12</v>
@@ -15411,7 +15478,7 @@
         <v>241</v>
       </c>
       <c r="M163" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N163" s="27"/>
       <c r="O163" s="27">
@@ -15463,7 +15530,7 @@
         <v>15395.489999999998</v>
       </c>
       <c r="AE163" s="38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF163" s="3"/>
       <c r="AG163" s="14"/>
@@ -15481,11 +15548,11 @@
     <row r="164" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>12</v>
@@ -15506,7 +15573,7 @@
         <v>241</v>
       </c>
       <c r="M164" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N164" s="27"/>
       <c r="O164" s="27">
@@ -15558,7 +15625,7 @@
         <v>15264.315000000002</v>
       </c>
       <c r="AE164" s="38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF164" s="3"/>
       <c r="AG164" s="14"/>
@@ -15576,11 +15643,11 @@
     <row r="165" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>12</v>
@@ -15601,7 +15668,7 @@
         <v>241</v>
       </c>
       <c r="M165" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N165" s="27"/>
       <c r="O165" s="27">
@@ -15653,7 +15720,7 @@
         <v>14775.915000000001</v>
       </c>
       <c r="AE165" s="38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF165" s="3"/>
       <c r="AG165" s="14"/>
@@ -15671,11 +15738,11 @@
     <row r="166" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>12</v>
@@ -15696,7 +15763,7 @@
         <v>239</v>
       </c>
       <c r="M166" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N166" s="27"/>
       <c r="O166" s="27">
@@ -15748,7 +15815,7 @@
         <v>14889.434999999998</v>
       </c>
       <c r="AE166" s="38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF166" s="3"/>
       <c r="AG166" s="14"/>
@@ -15766,11 +15833,11 @@
     <row r="167" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>12</v>
@@ -15791,7 +15858,7 @@
         <v>239</v>
       </c>
       <c r="M167" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N167" s="27"/>
       <c r="O167" s="27">
@@ -15843,7 +15910,7 @@
         <v>14290.815000000002</v>
       </c>
       <c r="AE167" s="38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF167" s="3"/>
       <c r="AG167" s="14"/>
@@ -15861,11 +15928,11 @@
     <row r="168" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>12</v>
@@ -15886,7 +15953,7 @@
         <v>239</v>
       </c>
       <c r="M168" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N168" s="27"/>
       <c r="O168" s="27">
@@ -15938,7 +16005,7 @@
         <v>14847.525000000001</v>
       </c>
       <c r="AE168" s="38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF168" s="3"/>
       <c r="AG168" s="14"/>
@@ -16027,7 +16094,7 @@
         <v>239</v>
       </c>
       <c r="M170" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N170" s="27"/>
       <c r="O170" s="27">
@@ -16120,7 +16187,7 @@
         <v>239</v>
       </c>
       <c r="M171" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N171" s="27"/>
       <c r="O171" s="27">
@@ -16213,7 +16280,7 @@
         <v>285</v>
       </c>
       <c r="M172" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N172" s="27"/>
       <c r="O172" s="27">
@@ -16306,7 +16373,7 @@
         <v>285</v>
       </c>
       <c r="M173" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N173" s="27"/>
       <c r="O173" s="27">
@@ -16399,7 +16466,7 @@
         <v>241</v>
       </c>
       <c r="M174" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N174" s="27"/>
       <c r="O174" s="27">
@@ -16492,7 +16559,7 @@
         <v>241</v>
       </c>
       <c r="M175" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N175" s="27"/>
       <c r="O175" s="27">
@@ -16631,7 +16698,7 @@
         <v>199</v>
       </c>
       <c r="M177" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N177" s="27"/>
       <c r="O177" s="27">
@@ -16724,7 +16791,7 @@
         <v>241</v>
       </c>
       <c r="M178" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N178" s="27"/>
       <c r="O178" s="27">
@@ -16796,7 +16863,7 @@
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>12</v>
@@ -16817,7 +16884,7 @@
         <v>241</v>
       </c>
       <c r="M179" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N179" s="27"/>
       <c r="O179" s="27">
@@ -16889,7 +16956,7 @@
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>12</v>
@@ -16910,7 +16977,7 @@
         <v>241</v>
       </c>
       <c r="M180" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N180" s="27"/>
       <c r="O180" s="27">
@@ -16982,7 +17049,7 @@
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>12</v>
@@ -17003,7 +17070,7 @@
         <v>240</v>
       </c>
       <c r="M181" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N181" s="27"/>
       <c r="O181" s="27">
@@ -17075,7 +17142,7 @@
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>12</v>
@@ -17096,7 +17163,7 @@
         <v>119</v>
       </c>
       <c r="M182" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N182" s="27"/>
       <c r="O182" s="27">
@@ -17210,11 +17277,11 @@
     <row r="184" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>12</v>
@@ -17233,7 +17300,7 @@
         <v>239</v>
       </c>
       <c r="M184" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N184" s="27"/>
       <c r="O184" s="27">
@@ -17301,11 +17368,11 @@
     <row r="185" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>12</v>
@@ -17324,7 +17391,7 @@
         <v>239</v>
       </c>
       <c r="M185" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N185" s="27"/>
       <c r="O185" s="27">
@@ -17392,11 +17459,11 @@
     <row r="186" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>12</v>
@@ -17415,7 +17482,7 @@
         <v>239</v>
       </c>
       <c r="M186" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N186" s="27"/>
       <c r="O186" s="27">
@@ -17483,11 +17550,11 @@
     <row r="187" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>12</v>
@@ -17506,7 +17573,7 @@
         <v>241</v>
       </c>
       <c r="M187" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N187" s="27"/>
       <c r="O187" s="27">
@@ -17574,11 +17641,11 @@
     <row r="188" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>12</v>
@@ -17597,7 +17664,7 @@
         <v>241</v>
       </c>
       <c r="M188" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N188" s="27"/>
       <c r="O188" s="27">
@@ -17665,11 +17732,11 @@
     <row r="189" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>12</v>
@@ -17688,7 +17755,7 @@
         <v>241</v>
       </c>
       <c r="M189" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N189" s="27"/>
       <c r="O189" s="27">
@@ -17756,11 +17823,11 @@
     <row r="190" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>12</v>
@@ -17779,7 +17846,7 @@
         <v>242</v>
       </c>
       <c r="M190" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N190" s="27"/>
       <c r="O190" s="27">
@@ -17847,11 +17914,11 @@
     <row r="191" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>12</v>
@@ -17870,7 +17937,7 @@
         <v>242</v>
       </c>
       <c r="M191" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N191" s="27"/>
       <c r="O191" s="27">
@@ -17938,11 +18005,11 @@
     <row r="192" spans="1:44" ht="32" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>12</v>
@@ -17961,7 +18028,7 @@
         <v>242</v>
       </c>
       <c r="M192" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N192" s="27"/>
       <c r="O192" s="27">
@@ -18026,7 +18093,7 @@
       <c r="AQ192" s="3"/>
       <c r="AR192" s="3"/>
     </row>
-    <row r="193" spans="1:31" ht="20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:44" ht="20" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="7"/>
@@ -18072,907 +18139,1988 @@
         <v>89749.329999999987</v>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="N196" s="3"/>
-      <c r="O196" s="129"/>
-    </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="N197" s="3"/>
-      <c r="O197" s="129"/>
-    </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="N198" s="3"/>
-      <c r="O198" s="129"/>
-    </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="N199" s="3"/>
-      <c r="O199" s="129"/>
-    </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AC200" s="17"/>
-      <c r="AD200" s="17"/>
-    </row>
-    <row r="201" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AC201" s="54" t="s">
-        <v>372</v>
-      </c>
-      <c r="AD201" s="54"/>
-      <c r="AE201" s="112" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AC202" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD202" s="17">
-        <f>SUM(AD122,AD101,AD91,AD87,AD76,AD66,AD149,)</f>
-        <v>1228994.7240000002</v>
-      </c>
-    </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="W203" s="17"/>
-      <c r="Y203" t="s">
-        <v>345</v>
-      </c>
-      <c r="AC203" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD203" s="17">
-        <f>AD143+AD131+AD116+AD109+AD98+AD83+AD161+AD169</f>
-        <v>966336.96</v>
-      </c>
-      <c r="AE203" s="96">
-        <f>SUM(O143,O131,O116,O109,O98,O83,O161)</f>
-        <v>4667.2510000000002</v>
-      </c>
-    </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="W204" s="17"/>
-      <c r="AC204" t="s">
+    <row r="194" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H194" s="60"/>
+      <c r="I194" s="60"/>
+      <c r="J194" s="62"/>
+      <c r="K194" s="3"/>
+      <c r="L194" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M194" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N194" s="27"/>
+      <c r="O194" s="27">
+        <v>90.381</v>
+      </c>
+      <c r="P194" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q194" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R194" s="28">
+        <v>550</v>
+      </c>
+      <c r="S194" s="28">
+        <v>0</v>
+      </c>
+      <c r="T194" s="28">
+        <v>0</v>
+      </c>
+      <c r="U194" s="28"/>
+      <c r="V194" s="28">
+        <v>550</v>
+      </c>
+      <c r="W194" s="28">
+        <f>O194*V194</f>
+        <v>49709.55</v>
+      </c>
+      <c r="X194" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y194" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="28"/>
+      <c r="AB194" s="28">
+        <f>SUM(X194:Z194)</f>
+        <v>660</v>
+      </c>
+      <c r="AC194" s="28">
+        <f>AB194*O194</f>
+        <v>59651.46</v>
+      </c>
+      <c r="AD194" s="28">
+        <f>AC194-W194</f>
+        <v>9941.9099999999962</v>
+      </c>
+      <c r="AE194" s="38"/>
+      <c r="AF194" s="3"/>
+      <c r="AG194" s="14"/>
+      <c r="AI194" s="3"/>
+      <c r="AJ194" s="3"/>
+      <c r="AK194" s="3"/>
+      <c r="AL194" s="3"/>
+      <c r="AM194" s="3"/>
+      <c r="AN194" s="3"/>
+      <c r="AO194" s="3"/>
+      <c r="AP194" s="3"/>
+      <c r="AQ194" s="3"/>
+      <c r="AR194" s="3"/>
+    </row>
+    <row r="195" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H195" s="60"/>
+      <c r="I195" s="60"/>
+      <c r="J195" s="62"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M195" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N195" s="27"/>
+      <c r="O195" s="27">
+        <v>91.6</v>
+      </c>
+      <c r="P195" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q195" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R195" s="28">
+        <v>550</v>
+      </c>
+      <c r="S195" s="28">
+        <v>0</v>
+      </c>
+      <c r="T195" s="28">
+        <v>0</v>
+      </c>
+      <c r="U195" s="28"/>
+      <c r="V195" s="28">
+        <v>550</v>
+      </c>
+      <c r="W195" s="28">
+        <f>O195*V195</f>
+        <v>50380</v>
+      </c>
+      <c r="X195" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y195" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="28"/>
+      <c r="AB195" s="28">
+        <f>SUM(X195:Z195)</f>
+        <v>660</v>
+      </c>
+      <c r="AC195" s="28">
+        <f>AB195*O195</f>
+        <v>60455.999999999993</v>
+      </c>
+      <c r="AD195" s="28">
+        <f>AC195-W195</f>
+        <v>10075.999999999993</v>
+      </c>
+      <c r="AE195" s="38"/>
+      <c r="AF195" s="3"/>
+      <c r="AG195" s="14"/>
+      <c r="AI195" s="3"/>
+      <c r="AJ195" s="3"/>
+      <c r="AK195" s="3"/>
+      <c r="AL195" s="3"/>
+      <c r="AM195" s="3"/>
+      <c r="AN195" s="3"/>
+      <c r="AO195" s="3"/>
+      <c r="AP195" s="3"/>
+      <c r="AQ195" s="3"/>
+      <c r="AR195" s="3"/>
+    </row>
+    <row r="196" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H196" s="60"/>
+      <c r="I196" s="60"/>
+      <c r="J196" s="62"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="M196" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N196" s="27"/>
+      <c r="O196" s="27">
+        <v>91.391999999999996</v>
+      </c>
+      <c r="P196" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q196" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R196" s="28">
+        <v>550</v>
+      </c>
+      <c r="S196" s="28">
+        <v>0</v>
+      </c>
+      <c r="T196" s="28">
+        <v>0</v>
+      </c>
+      <c r="U196" s="28"/>
+      <c r="V196" s="28">
+        <v>550</v>
+      </c>
+      <c r="W196" s="28">
+        <f>O196*V196</f>
+        <v>50265.599999999999</v>
+      </c>
+      <c r="X196" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y196" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="28"/>
+      <c r="AB196" s="28">
+        <f>SUM(X196:Z196)</f>
+        <v>660</v>
+      </c>
+      <c r="AC196" s="28">
+        <f>AB196*O196</f>
+        <v>60318.719999999994</v>
+      </c>
+      <c r="AD196" s="28">
+        <f>AC196-W196</f>
+        <v>10053.119999999995</v>
+      </c>
+      <c r="AE196" s="38"/>
+      <c r="AF196" s="3"/>
+      <c r="AG196" s="14"/>
+      <c r="AI196" s="3"/>
+      <c r="AJ196" s="3"/>
+      <c r="AK196" s="3"/>
+      <c r="AL196" s="3"/>
+      <c r="AM196" s="3"/>
+      <c r="AN196" s="3"/>
+      <c r="AO196" s="3"/>
+      <c r="AP196" s="3"/>
+      <c r="AQ196" s="3"/>
+      <c r="AR196" s="3"/>
+    </row>
+    <row r="197" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H197" s="60"/>
+      <c r="I197" s="60"/>
+      <c r="J197" s="62"/>
+      <c r="K197" s="3"/>
+      <c r="L197" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="M197" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N197" s="27"/>
+      <c r="O197" s="27">
+        <v>91.721000000000004</v>
+      </c>
+      <c r="P197" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q197" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R197" s="28">
+        <v>550</v>
+      </c>
+      <c r="S197" s="28">
+        <v>0</v>
+      </c>
+      <c r="T197" s="28">
+        <v>0</v>
+      </c>
+      <c r="U197" s="28"/>
+      <c r="V197" s="28">
+        <v>550</v>
+      </c>
+      <c r="W197" s="28">
+        <f>O197*V197</f>
+        <v>50446.55</v>
+      </c>
+      <c r="X197" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y197" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="28"/>
+      <c r="AB197" s="28">
+        <f>SUM(X197:Z197)</f>
+        <v>660</v>
+      </c>
+      <c r="AC197" s="28">
+        <f>AB197*O197</f>
+        <v>60535.86</v>
+      </c>
+      <c r="AD197" s="28">
+        <f>AC197-W197</f>
+        <v>10089.309999999998</v>
+      </c>
+      <c r="AE197" s="38"/>
+      <c r="AF197" s="3"/>
+      <c r="AG197" s="14"/>
+      <c r="AI197" s="3"/>
+      <c r="AJ197" s="3"/>
+      <c r="AK197" s="3"/>
+      <c r="AL197" s="3"/>
+      <c r="AM197" s="3"/>
+      <c r="AN197" s="3"/>
+      <c r="AO197" s="3"/>
+      <c r="AP197" s="3"/>
+      <c r="AQ197" s="3"/>
+      <c r="AR197" s="3"/>
+    </row>
+    <row r="198" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H198" s="60"/>
+      <c r="I198" s="60"/>
+      <c r="J198" s="62"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="M198" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N198" s="27"/>
+      <c r="O198" s="27">
+        <v>92.772999999999996</v>
+      </c>
+      <c r="P198" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q198" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R198" s="28">
+        <v>550</v>
+      </c>
+      <c r="S198" s="28">
+        <v>0</v>
+      </c>
+      <c r="T198" s="28">
+        <v>0</v>
+      </c>
+      <c r="U198" s="28"/>
+      <c r="V198" s="28">
+        <v>550</v>
+      </c>
+      <c r="W198" s="28">
+        <f t="shared" ref="W198:W201" si="90">O198*V198</f>
+        <v>51025.15</v>
+      </c>
+      <c r="X198" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y198" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="28"/>
+      <c r="AB198" s="28">
+        <f>SUM(X198:Z198)</f>
+        <v>660</v>
+      </c>
+      <c r="AC198" s="28">
+        <f>AB198*O198</f>
+        <v>61230.18</v>
+      </c>
+      <c r="AD198" s="28">
+        <f>AC198-W198</f>
+        <v>10205.029999999999</v>
+      </c>
+      <c r="AE198" s="38"/>
+      <c r="AF198" s="3"/>
+      <c r="AG198" s="14"/>
+      <c r="AI198" s="3"/>
+      <c r="AJ198" s="3"/>
+      <c r="AK198" s="3"/>
+      <c r="AL198" s="3"/>
+      <c r="AM198" s="3"/>
+      <c r="AN198" s="3"/>
+      <c r="AO198" s="3"/>
+      <c r="AP198" s="3"/>
+      <c r="AQ198" s="3"/>
+      <c r="AR198" s="3"/>
+    </row>
+    <row r="199" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H199" s="60"/>
+      <c r="I199" s="60"/>
+      <c r="J199" s="62"/>
+      <c r="K199" s="3"/>
+      <c r="L199" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="M199" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N199" s="27"/>
+      <c r="O199" s="27">
+        <v>90.647999999999996</v>
+      </c>
+      <c r="P199" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q199" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R199" s="28">
+        <v>550</v>
+      </c>
+      <c r="S199" s="28">
+        <v>0</v>
+      </c>
+      <c r="T199" s="28">
+        <v>0</v>
+      </c>
+      <c r="U199" s="28"/>
+      <c r="V199" s="28">
+        <v>550</v>
+      </c>
+      <c r="W199" s="28">
+        <f t="shared" si="90"/>
+        <v>49856.4</v>
+      </c>
+      <c r="X199" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y199" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="28"/>
+      <c r="AB199" s="28">
+        <f>SUM(X199:Z199)</f>
+        <v>660</v>
+      </c>
+      <c r="AC199" s="28">
+        <f>AB199*O199</f>
+        <v>59827.68</v>
+      </c>
+      <c r="AD199" s="28">
+        <f>AC199-W199</f>
+        <v>9971.2799999999988</v>
+      </c>
+      <c r="AE199" s="38"/>
+      <c r="AF199" s="3"/>
+      <c r="AG199" s="14"/>
+      <c r="AI199" s="3"/>
+      <c r="AJ199" s="3"/>
+      <c r="AK199" s="3"/>
+      <c r="AL199" s="3"/>
+      <c r="AM199" s="3"/>
+      <c r="AN199" s="3"/>
+      <c r="AO199" s="3"/>
+      <c r="AP199" s="3"/>
+      <c r="AQ199" s="3"/>
+      <c r="AR199" s="3"/>
+    </row>
+    <row r="200" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H200" s="60"/>
+      <c r="I200" s="60"/>
+      <c r="J200" s="62"/>
+      <c r="K200" s="3"/>
+      <c r="L200" s="27"/>
+      <c r="M200" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N200" s="27"/>
+      <c r="O200" s="27">
+        <v>90</v>
+      </c>
+      <c r="P200" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q200" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R200" s="28">
+        <v>550</v>
+      </c>
+      <c r="S200" s="28">
+        <v>0</v>
+      </c>
+      <c r="T200" s="28">
+        <v>0</v>
+      </c>
+      <c r="U200" s="28"/>
+      <c r="V200" s="28">
+        <v>550</v>
+      </c>
+      <c r="W200" s="28">
+        <f t="shared" si="90"/>
+        <v>49500</v>
+      </c>
+      <c r="X200" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y200" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="28"/>
+      <c r="AB200" s="28">
+        <f>SUM(X200:Z200)</f>
+        <v>660</v>
+      </c>
+      <c r="AC200" s="28">
+        <f>AB200*O200</f>
+        <v>59400</v>
+      </c>
+      <c r="AD200" s="28">
+        <f>AC200-W200</f>
+        <v>9900</v>
+      </c>
+      <c r="AE200" s="38"/>
+      <c r="AF200" s="3"/>
+      <c r="AG200" s="14"/>
+      <c r="AI200" s="3"/>
+      <c r="AJ200" s="3"/>
+      <c r="AK200" s="3"/>
+      <c r="AL200" s="3"/>
+      <c r="AM200" s="3"/>
+      <c r="AN200" s="3"/>
+      <c r="AO200" s="3"/>
+      <c r="AP200" s="3"/>
+      <c r="AQ200" s="3"/>
+      <c r="AR200" s="3"/>
+    </row>
+    <row r="201" spans="1:44" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H201" s="60"/>
+      <c r="I201" s="60"/>
+      <c r="J201" s="62"/>
+      <c r="K201" s="3"/>
+      <c r="L201" s="27"/>
+      <c r="M201" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N201" s="27"/>
+      <c r="O201" s="27">
+        <v>90</v>
+      </c>
+      <c r="P201" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q201" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R201" s="28">
+        <v>550</v>
+      </c>
+      <c r="S201" s="28">
+        <v>0</v>
+      </c>
+      <c r="T201" s="28">
+        <v>0</v>
+      </c>
+      <c r="U201" s="28"/>
+      <c r="V201" s="28">
+        <v>550</v>
+      </c>
+      <c r="W201" s="28">
+        <f t="shared" si="90"/>
+        <v>49500</v>
+      </c>
+      <c r="X201" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y201" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z201" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA201" s="28"/>
+      <c r="AB201" s="28">
+        <f>SUM(X201:Z201)</f>
+        <v>660</v>
+      </c>
+      <c r="AC201" s="28">
+        <f>AB201*O201</f>
+        <v>59400</v>
+      </c>
+      <c r="AD201" s="28">
+        <f>AC201-W201</f>
+        <v>9900</v>
+      </c>
+      <c r="AE201" s="38"/>
+      <c r="AF201" s="3"/>
+      <c r="AG201" s="14"/>
+      <c r="AI201" s="3"/>
+      <c r="AJ201" s="3"/>
+      <c r="AK201" s="3"/>
+      <c r="AL201" s="3"/>
+      <c r="AM201" s="3"/>
+      <c r="AN201" s="3"/>
+      <c r="AO201" s="3"/>
+      <c r="AP201" s="3"/>
+      <c r="AQ201" s="3"/>
+      <c r="AR201" s="3"/>
+    </row>
+    <row r="202" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A202" s="3"/>
+      <c r="B202" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H202" s="60"/>
+      <c r="I202" s="60"/>
+      <c r="J202" s="62"/>
+      <c r="K202" s="3"/>
+      <c r="L202" s="27"/>
+      <c r="M202" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N202" s="27"/>
+      <c r="O202" s="27">
+        <v>90</v>
+      </c>
+      <c r="P202" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q202" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R202" s="28">
+        <v>550</v>
+      </c>
+      <c r="S202" s="28">
+        <v>0</v>
+      </c>
+      <c r="T202" s="28">
+        <v>0</v>
+      </c>
+      <c r="U202" s="28"/>
+      <c r="V202" s="28">
+        <v>550</v>
+      </c>
+      <c r="W202" s="28">
+        <f>O202*V202</f>
+        <v>49500</v>
+      </c>
+      <c r="X202" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y202" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z202" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA202" s="28"/>
+      <c r="AB202" s="28">
+        <f>SUM(X202:Z202)</f>
+        <v>660</v>
+      </c>
+      <c r="AC202" s="28">
+        <f>AB202*O202</f>
+        <v>59400</v>
+      </c>
+      <c r="AD202" s="28">
+        <f>AC202-W202</f>
+        <v>9900</v>
+      </c>
+      <c r="AE202" s="38"/>
+      <c r="AF202" s="3"/>
+      <c r="AG202" s="14"/>
+      <c r="AI202" s="3"/>
+      <c r="AJ202" s="3"/>
+      <c r="AK202" s="3"/>
+      <c r="AL202" s="3"/>
+      <c r="AM202" s="3"/>
+      <c r="AN202" s="3"/>
+      <c r="AO202" s="3"/>
+      <c r="AP202" s="3"/>
+      <c r="AQ202" s="3"/>
+      <c r="AR202" s="3"/>
+    </row>
+    <row r="203" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H203" s="60"/>
+      <c r="I203" s="60"/>
+      <c r="J203" s="62"/>
+      <c r="K203" s="3"/>
+      <c r="L203" s="27"/>
+      <c r="M203" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N203" s="27"/>
+      <c r="O203" s="27">
+        <v>90</v>
+      </c>
+      <c r="P203" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q203" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R203" s="28">
+        <v>550</v>
+      </c>
+      <c r="S203" s="28">
+        <v>0</v>
+      </c>
+      <c r="T203" s="28">
+        <v>0</v>
+      </c>
+      <c r="U203" s="28"/>
+      <c r="V203" s="28">
+        <v>550</v>
+      </c>
+      <c r="W203" s="28">
+        <f>O203*V203</f>
+        <v>49500</v>
+      </c>
+      <c r="X203" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y203" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA203" s="28"/>
+      <c r="AB203" s="28">
+        <f>SUM(X203:Z203)</f>
+        <v>660</v>
+      </c>
+      <c r="AC203" s="28">
+        <f>AB203*O203</f>
+        <v>59400</v>
+      </c>
+      <c r="AD203" s="28">
+        <f>AC203-W203</f>
+        <v>9900</v>
+      </c>
+      <c r="AE203" s="38"/>
+      <c r="AF203" s="3"/>
+      <c r="AG203" s="14"/>
+      <c r="AI203" s="3"/>
+      <c r="AJ203" s="3"/>
+      <c r="AK203" s="3"/>
+      <c r="AL203" s="3"/>
+      <c r="AM203" s="3"/>
+      <c r="AN203" s="3"/>
+      <c r="AO203" s="3"/>
+      <c r="AP203" s="3"/>
+      <c r="AQ203" s="3"/>
+      <c r="AR203" s="3"/>
+    </row>
+    <row r="204" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H204" s="60"/>
+      <c r="I204" s="60"/>
+      <c r="J204" s="62"/>
+      <c r="K204" s="3"/>
+      <c r="L204" s="27"/>
+      <c r="M204" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N204" s="27"/>
+      <c r="O204" s="27">
+        <v>90</v>
+      </c>
+      <c r="P204" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q204" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R204" s="28">
+        <v>550</v>
+      </c>
+      <c r="S204" s="28">
+        <v>0</v>
+      </c>
+      <c r="T204" s="28">
+        <v>0</v>
+      </c>
+      <c r="U204" s="28"/>
+      <c r="V204" s="28">
+        <v>550</v>
+      </c>
+      <c r="W204" s="28">
+        <f>O204*V204</f>
+        <v>49500</v>
+      </c>
+      <c r="X204" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y204" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z204" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA204" s="28"/>
+      <c r="AB204" s="28">
+        <f>SUM(X204:Z204)</f>
+        <v>660</v>
+      </c>
+      <c r="AC204" s="28">
+        <f>AB204*O204</f>
+        <v>59400</v>
+      </c>
+      <c r="AD204" s="28">
+        <f>AC204-W204</f>
+        <v>9900</v>
+      </c>
+      <c r="AE204" s="38"/>
+      <c r="AF204" s="3"/>
+      <c r="AG204" s="14"/>
+      <c r="AI204" s="3"/>
+      <c r="AJ204" s="3"/>
+      <c r="AK204" s="3"/>
+      <c r="AL204" s="3"/>
+      <c r="AM204" s="3"/>
+      <c r="AN204" s="3"/>
+      <c r="AO204" s="3"/>
+      <c r="AP204" s="3"/>
+      <c r="AQ204" s="3"/>
+      <c r="AR204" s="3"/>
+    </row>
+    <row r="205" spans="1:44" ht="32" x14ac:dyDescent="0.2">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H205" s="60"/>
+      <c r="I205" s="60"/>
+      <c r="J205" s="62"/>
+      <c r="K205" s="3"/>
+      <c r="L205" s="27"/>
+      <c r="M205" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="N205" s="27"/>
+      <c r="O205" s="27">
+        <v>90</v>
+      </c>
+      <c r="P205" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q205" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="R205" s="28">
+        <v>550</v>
+      </c>
+      <c r="S205" s="28">
+        <v>0</v>
+      </c>
+      <c r="T205" s="28">
+        <v>0</v>
+      </c>
+      <c r="U205" s="28"/>
+      <c r="V205" s="28">
+        <v>550</v>
+      </c>
+      <c r="W205" s="28">
+        <f>O205*V205</f>
+        <v>49500</v>
+      </c>
+      <c r="X205" s="28">
+        <v>660</v>
+      </c>
+      <c r="Y205" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="28"/>
+      <c r="AB205" s="28">
+        <f>SUM(X205:Z205)</f>
+        <v>660</v>
+      </c>
+      <c r="AC205" s="28">
+        <f>AB205*O205</f>
+        <v>59400</v>
+      </c>
+      <c r="AD205" s="28">
+        <f>AC205-W205</f>
+        <v>9900</v>
+      </c>
+      <c r="AE205" s="38"/>
+      <c r="AF205" s="3"/>
+      <c r="AG205" s="14"/>
+      <c r="AI205" s="3"/>
+      <c r="AJ205" s="3"/>
+      <c r="AK205" s="3"/>
+      <c r="AL205" s="3"/>
+      <c r="AM205" s="3"/>
+      <c r="AN205" s="3"/>
+      <c r="AO205" s="3"/>
+      <c r="AP205" s="3"/>
+      <c r="AQ205" s="3"/>
+      <c r="AR205" s="3"/>
+    </row>
+    <row r="206" spans="1:44" ht="20" x14ac:dyDescent="0.25">
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
+      <c r="G206" s="7"/>
+      <c r="H206" s="7"/>
+      <c r="I206" s="60"/>
+      <c r="J206" s="62"/>
+      <c r="K206" s="7"/>
+      <c r="L206" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M206" s="24"/>
+      <c r="N206" s="24"/>
+      <c r="O206" s="24">
+        <f>+SUM(O194:O205)</f>
+        <v>1088.5149999999999</v>
+      </c>
+      <c r="P206" s="8"/>
+      <c r="Q206" s="24"/>
+      <c r="R206" s="24"/>
+      <c r="S206" s="24"/>
+      <c r="T206" s="24"/>
+      <c r="U206" s="24"/>
+      <c r="V206" s="24"/>
+      <c r="W206" s="25">
+        <f>+SUM(W194:W205)</f>
+        <v>598683.25</v>
+      </c>
+      <c r="X206" s="24"/>
+      <c r="Y206" s="24"/>
+      <c r="Z206" s="24"/>
+      <c r="AA206" s="24"/>
+      <c r="AB206" s="24"/>
+      <c r="AC206" s="25">
+        <f>+SUM(AC194:AC205)</f>
+        <v>718419.89999999991</v>
+      </c>
+      <c r="AD206" s="25">
+        <f>+SUM(AD194:AD205)</f>
+        <v>119736.64999999998</v>
+      </c>
+    </row>
+    <row r="207" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="W207" s="17"/>
+      <c r="AC207" t="s">
         <v>269</v>
       </c>
-      <c r="AD204" s="17">
+      <c r="AD207" s="17">
         <f>SUM(AD146,AD118,AD153)</f>
         <v>107931.84000000001</v>
       </c>
-      <c r="AE204" s="96">
+      <c r="AE207" s="96">
         <f>SUM(O146,O118,O153)</f>
         <v>553.41</v>
       </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="W205" s="17"/>
-      <c r="Y205" s="15"/>
-      <c r="AD205" s="17"/>
-      <c r="AE205" s="43"/>
-    </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="W206" s="17"/>
-      <c r="Y206" s="17"/>
-      <c r="Z206" s="43"/>
-      <c r="AA206" s="43"/>
-      <c r="AB206" s="106"/>
-      <c r="AC206" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="AD206" s="54"/>
-      <c r="AE206" s="96" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="W207" s="17"/>
-      <c r="AC207" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD207" s="17"/>
-      <c r="AE207" s="43"/>
-    </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:44" x14ac:dyDescent="0.2">
       <c r="W208" s="17"/>
-      <c r="Z208" s="43"/>
-      <c r="AA208" s="43"/>
-      <c r="AC208" t="s">
-        <v>264</v>
-      </c>
-      <c r="AD208" s="17">
-        <f>SUM(AD176,AD183)</f>
-        <v>135400.12500000003</v>
-      </c>
-      <c r="AE208" s="96"/>
+      <c r="Y208" s="15"/>
+      <c r="AD208" s="17"/>
+      <c r="AE208" s="43"/>
     </row>
     <row r="209" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W209" s="17"/>
       <c r="Y209" s="17"/>
-      <c r="AC209" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD209" s="17"/>
-      <c r="AE209" s="96"/>
+      <c r="Z209" s="43"/>
+      <c r="AA209" s="43"/>
+      <c r="AB209" s="106"/>
+      <c r="AC209" s="54" t="s">
+        <v>372</v>
+      </c>
+      <c r="AD209" s="54"/>
+      <c r="AE209" s="96" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="210" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W210" s="17"/>
+      <c r="AC210" t="s">
+        <v>265</v>
+      </c>
       <c r="AD210" s="17"/>
-      <c r="AE210" s="96"/>
+      <c r="AE210" s="43"/>
     </row>
     <row r="211" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="AD211" s="17"/>
+      <c r="W211" s="17"/>
+      <c r="Z211" s="43"/>
+      <c r="AA211" s="43"/>
+      <c r="AC211" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD211" s="17">
+        <f>SUM(AD176,AD183,AD193,AD206)</f>
+        <v>344886.10499999998</v>
+      </c>
       <c r="AE211" s="96"/>
     </row>
     <row r="212" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W212" s="17"/>
-      <c r="AC212" s="17"/>
+      <c r="Y212" s="17"/>
+      <c r="AC212" t="s">
+        <v>269</v>
+      </c>
+      <c r="AD212" s="17"/>
       <c r="AE212" s="96"/>
     </row>
     <row r="213" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="AB213" s="17"/>
-      <c r="AC213" s="17"/>
+      <c r="W213" s="17"/>
+      <c r="AD213" s="17"/>
       <c r="AE213" s="96"/>
     </row>
     <row r="214" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="P214" s="36"/>
-      <c r="AB214" s="17"/>
-      <c r="AE214" s="43"/>
+      <c r="AD214" s="17"/>
+      <c r="AE214" s="96"/>
     </row>
     <row r="215" spans="16:36" x14ac:dyDescent="0.2">
       <c r="W215" s="17"/>
-      <c r="AB215" s="17"/>
-      <c r="AE215" s="43"/>
+      <c r="AC215" s="17"/>
+      <c r="AE215" s="96"/>
     </row>
     <row r="216" spans="16:36" x14ac:dyDescent="0.2">
       <c r="AB216" s="17"/>
-      <c r="AE216" s="43"/>
+      <c r="AC216" s="17"/>
+      <c r="AE216" s="96"/>
     </row>
     <row r="217" spans="16:36" x14ac:dyDescent="0.2">
+      <c r="P217" s="36"/>
       <c r="AB217" s="17"/>
       <c r="AE217" s="43"/>
     </row>
     <row r="218" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="Q218" s="17"/>
+      <c r="W218" s="17"/>
       <c r="AB218" s="17"/>
-      <c r="AF218" s="88" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG218" s="88"/>
-      <c r="AH218" s="88"/>
-      <c r="AI218" s="88"/>
-      <c r="AJ218" s="88"/>
-    </row>
-    <row r="219" spans="16:36" ht="16" x14ac:dyDescent="0.2">
-      <c r="Q219" s="17"/>
+      <c r="AE218" s="43"/>
+    </row>
+    <row r="219" spans="16:36" x14ac:dyDescent="0.2">
       <c r="AB219" s="17"/>
-      <c r="AF219" s="83" t="s">
-        <v>243</v>
-      </c>
-      <c r="AG219" s="122" t="s">
-        <v>381</v>
-      </c>
-      <c r="AH219" s="123" t="s">
-        <v>244</v>
-      </c>
-      <c r="AI219" s="123"/>
-      <c r="AJ219" s="82" t="s">
-        <v>382</v>
-      </c>
+      <c r="AE219" s="43"/>
     </row>
     <row r="220" spans="16:36" x14ac:dyDescent="0.2">
-      <c r="Q220" s="17"/>
       <c r="AB220" s="17"/>
-      <c r="AF220" s="80"/>
-      <c r="AG220" s="124"/>
-      <c r="AH220" s="52"/>
-      <c r="AI220" s="123"/>
-      <c r="AJ220" s="52"/>
+      <c r="AE220" s="43"/>
     </row>
     <row r="221" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q221" s="17"/>
       <c r="AB221" s="17"/>
-      <c r="AF221" s="80"/>
-      <c r="AG221" s="124"/>
-      <c r="AH221" s="52"/>
-      <c r="AI221" s="123"/>
-      <c r="AJ221" s="52"/>
-    </row>
-    <row r="222" spans="16:36" x14ac:dyDescent="0.2">
+      <c r="AF221" s="88" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG221" s="88"/>
+      <c r="AH221" s="88"/>
+      <c r="AI221" s="88"/>
+      <c r="AJ221" s="88"/>
+    </row>
+    <row r="222" spans="16:36" ht="16" x14ac:dyDescent="0.2">
       <c r="Q222" s="17"/>
       <c r="AB222" s="17"/>
-      <c r="AF222" s="80"/>
-      <c r="AG222" s="124"/>
-      <c r="AH222" s="52"/>
-      <c r="AI222" s="123"/>
-      <c r="AJ222" s="52"/>
+      <c r="AF222" s="83" t="s">
+        <v>243</v>
+      </c>
+      <c r="AG222" s="121" t="s">
+        <v>380</v>
+      </c>
+      <c r="AH222" s="122" t="s">
+        <v>244</v>
+      </c>
+      <c r="AI222" s="122"/>
+      <c r="AJ222" s="82" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="223" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q223" s="17"/>
       <c r="AB223" s="17"/>
-      <c r="AF223" s="80">
-        <v>445000</v>
-      </c>
-      <c r="AG223" s="125">
-        <v>46091</v>
-      </c>
-      <c r="AH223" s="52">
-        <v>810</v>
-      </c>
-      <c r="AI223" s="123"/>
-      <c r="AJ223" s="52" t="s">
-        <v>99</v>
-      </c>
+      <c r="AF223" s="80"/>
+      <c r="AG223" s="123"/>
+      <c r="AH223" s="52"/>
+      <c r="AI223" s="122"/>
+      <c r="AJ223" s="52"/>
     </row>
     <row r="224" spans="16:36" x14ac:dyDescent="0.2">
       <c r="Q224" s="17"/>
       <c r="AB224" s="17"/>
       <c r="AF224" s="80">
-        <v>290000</v>
-      </c>
-      <c r="AG224" s="125">
-        <v>46072</v>
-      </c>
-      <c r="AH224" s="52">
-        <v>540</v>
-      </c>
-      <c r="AI224" s="123"/>
+        <v>297000</v>
+      </c>
+      <c r="AG224" s="123">
+        <v>46121</v>
+      </c>
+      <c r="AH224" s="52" t="s">
+        <v>419</v>
+      </c>
+      <c r="AI224" s="122"/>
       <c r="AJ224" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="225" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="225" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q225" s="17"/>
       <c r="AB225" s="17"/>
       <c r="AF225" s="80">
-        <v>294000</v>
-      </c>
-      <c r="AG225" s="125">
-        <v>46043</v>
+        <v>297000</v>
+      </c>
+      <c r="AG225" s="123" t="s">
+        <v>415</v>
       </c>
       <c r="AH225" s="52">
         <v>540</v>
       </c>
-      <c r="AI225" s="52"/>
+      <c r="AI225" s="122"/>
       <c r="AJ225" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="226" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="226" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q226" s="17"/>
       <c r="AB226" s="17"/>
       <c r="AF226" s="80">
-        <v>143100</v>
-      </c>
-      <c r="AG226" s="125">
-        <v>46010</v>
+        <v>445000</v>
+      </c>
+      <c r="AG226" s="124">
+        <v>46091</v>
       </c>
       <c r="AH226" s="52">
-        <v>270</v>
-      </c>
-      <c r="AI226" s="52"/>
+        <v>810</v>
+      </c>
+      <c r="AI226" s="122"/>
       <c r="AJ226" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="227" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="227" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q227" s="17"/>
       <c r="AB227" s="17"/>
       <c r="AF227" s="80">
-        <v>190800</v>
-      </c>
-      <c r="AG227" s="125">
-        <v>46007</v>
+        <v>290000</v>
+      </c>
+      <c r="AG227" s="124">
+        <v>46072</v>
       </c>
       <c r="AH227" s="52">
-        <v>360</v>
-      </c>
-      <c r="AI227" s="52"/>
+        <v>540</v>
+      </c>
+      <c r="AI227" s="122"/>
       <c r="AJ227" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="228" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="228" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q228" s="17"/>
       <c r="AB228" s="17"/>
       <c r="AF228" s="80">
-        <v>47700</v>
-      </c>
-      <c r="AG228" s="125">
-        <v>45993</v>
+        <v>294000</v>
+      </c>
+      <c r="AG228" s="124">
+        <v>46043</v>
       </c>
       <c r="AH228" s="52">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AI228" s="52"/>
       <c r="AJ228" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="229" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="229" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q229" s="17"/>
       <c r="AB229" s="17"/>
       <c r="AF229" s="80">
-        <v>286000</v>
-      </c>
-      <c r="AG229" s="125">
-        <v>45979</v>
+        <v>143100</v>
+      </c>
+      <c r="AG229" s="124">
+        <v>46010</v>
       </c>
       <c r="AH229" s="52">
-        <v>540</v>
+        <v>270</v>
       </c>
       <c r="AI229" s="52"/>
       <c r="AJ229" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="230" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="230" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q230" s="17"/>
       <c r="AB230" s="17"/>
       <c r="AF230" s="80">
-        <v>145000</v>
-      </c>
-      <c r="AG230" s="125">
-        <v>45973</v>
+        <v>190800</v>
+      </c>
+      <c r="AG230" s="124">
+        <v>46007</v>
       </c>
       <c r="AH230" s="52">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="AI230" s="52"/>
       <c r="AJ230" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="231" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="231" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q231" s="17"/>
       <c r="AB231" s="17"/>
-      <c r="AE231" s="43"/>
       <c r="AF231" s="80">
-        <v>541800</v>
-      </c>
-      <c r="AG231" s="125">
-        <v>45960</v>
+        <v>47700</v>
+      </c>
+      <c r="AG231" s="124">
+        <v>45993</v>
       </c>
       <c r="AH231" s="52">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI231" s="52"/>
       <c r="AJ231" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="232" spans="17:44" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="AN231" t="s">
+        <v>406</v>
+      </c>
+      <c r="AP231" t="s">
+        <v>408</v>
+      </c>
+      <c r="AQ231" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="232" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q232" s="17"/>
       <c r="AB232" s="17"/>
       <c r="AF232" s="80">
-        <v>2089</v>
-      </c>
-      <c r="AG232" s="125">
-        <v>45954</v>
-      </c>
-      <c r="AH232" s="52" t="s">
-        <v>294</v>
+        <v>286000</v>
+      </c>
+      <c r="AG232" s="124">
+        <v>45979</v>
+      </c>
+      <c r="AH232" s="52">
+        <v>540</v>
       </c>
       <c r="AI232" s="52"/>
       <c r="AJ232" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="233" spans="17:44" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="AN232" t="s">
+        <v>407</v>
+      </c>
+      <c r="AO232">
+        <v>150</v>
+      </c>
+      <c r="AP232" t="s">
+        <v>409</v>
+      </c>
+      <c r="AQ232" s="15">
+        <f>13*150</f>
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="233" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q233" s="17"/>
+      <c r="AB233" s="17"/>
       <c r="AF233" s="80">
-        <v>540000</v>
-      </c>
-      <c r="AG233" s="125">
-        <v>45951</v>
+        <v>145000</v>
+      </c>
+      <c r="AG233" s="124">
+        <v>45973</v>
       </c>
       <c r="AH233" s="52">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AI233" s="52"/>
       <c r="AJ233" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="234" spans="17:44" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="AN233" t="s">
+        <v>410</v>
+      </c>
+      <c r="AO233">
+        <v>7</v>
+      </c>
+      <c r="AP233" t="s">
+        <v>411</v>
+      </c>
+      <c r="AQ233" s="15">
+        <f>330*7</f>
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="234" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q234" s="17"/>
+      <c r="AB234" s="17"/>
+      <c r="AE234" s="43"/>
       <c r="AF234" s="80">
-        <v>99000</v>
-      </c>
-      <c r="AG234" s="125">
-        <v>45950</v>
+        <v>541800</v>
+      </c>
+      <c r="AG234" s="124">
+        <v>45960</v>
       </c>
       <c r="AH234" s="52">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AI234" s="52"/>
       <c r="AJ234" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="235" spans="17:44" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="AN234" t="s">
+        <v>412</v>
+      </c>
+      <c r="AO234">
+        <v>6</v>
+      </c>
+      <c r="AP234" t="s">
+        <v>411</v>
+      </c>
+      <c r="AQ234" s="15">
+        <f>290*6</f>
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="235" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q235" s="17"/>
+      <c r="AB235" s="17"/>
       <c r="AF235" s="80">
-        <v>530000</v>
-      </c>
-      <c r="AG235" s="125">
-        <v>45939</v>
-      </c>
-      <c r="AH235" s="52">
-        <v>990</v>
-      </c>
-      <c r="AI235" s="123"/>
+        <v>2089</v>
+      </c>
+      <c r="AG235" s="124">
+        <v>45954</v>
+      </c>
+      <c r="AH235" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI235" s="52"/>
       <c r="AJ235" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="236" spans="17:44" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="AN235" t="s">
+        <v>413</v>
+      </c>
+      <c r="AO235">
+        <v>5</v>
+      </c>
+      <c r="AP235" t="s">
+        <v>411</v>
+      </c>
+      <c r="AQ235" s="15">
+        <f>320*5</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="236" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q236" s="17"/>
       <c r="AF236" s="80">
-        <v>400000</v>
-      </c>
-      <c r="AG236" s="125">
-        <v>45915</v>
+        <v>540000</v>
+      </c>
+      <c r="AG236" s="124">
+        <v>45951</v>
       </c>
       <c r="AH236" s="52">
-        <v>720</v>
-      </c>
-      <c r="AI236" s="123"/>
+        <v>1000</v>
+      </c>
+      <c r="AI236" s="52"/>
       <c r="AJ236" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="237" spans="17:44" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="AN236" t="s">
+        <v>414</v>
+      </c>
+      <c r="AO236">
+        <v>2</v>
+      </c>
+      <c r="AP236" t="s">
+        <v>411</v>
+      </c>
+      <c r="AQ236" s="15">
+        <f>1650*2</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="237" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q237" s="17"/>
       <c r="AF237" s="80">
-        <v>1395</v>
-      </c>
-      <c r="AG237" s="125">
-        <v>45904</v>
-      </c>
-      <c r="AH237" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="AI237" s="123"/>
+        <v>99000</v>
+      </c>
+      <c r="AG237" s="124">
+        <v>45950</v>
+      </c>
+      <c r="AH237" s="52">
+        <v>180</v>
+      </c>
+      <c r="AI237" s="52"/>
       <c r="AJ237" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="238" spans="17:44" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="AQ237" s="15"/>
+    </row>
+    <row r="238" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q238" s="17"/>
-      <c r="W238" s="17"/>
-      <c r="AD238" s="17"/>
-      <c r="AE238" s="43"/>
       <c r="AF238" s="80">
-        <v>51300</v>
-      </c>
-      <c r="AG238" s="125">
-        <v>45904</v>
+        <v>530000</v>
+      </c>
+      <c r="AG238" s="124">
+        <v>45939</v>
       </c>
       <c r="AH238" s="52">
-        <v>90</v>
-      </c>
-      <c r="AI238" s="123"/>
+        <v>990</v>
+      </c>
+      <c r="AI238" s="122"/>
       <c r="AJ238" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AP238" s="15"/>
-    </row>
-    <row r="239" spans="17:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AP238" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ238" s="15">
+        <f>SUM(AQ232:AQ236)</f>
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="239" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q239" s="17"/>
-      <c r="Z239" t="s">
-        <v>223</v>
-      </c>
       <c r="AF239" s="80">
-        <v>307760</v>
-      </c>
-      <c r="AG239" s="125">
-        <v>43313</v>
+        <v>400000</v>
+      </c>
+      <c r="AG239" s="124">
+        <v>45915</v>
       </c>
       <c r="AH239" s="52">
-        <v>540</v>
-      </c>
-      <c r="AI239" s="123"/>
+        <v>720</v>
+      </c>
+      <c r="AI239" s="122"/>
       <c r="AJ239" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="240" spans="17:44" x14ac:dyDescent="0.2">
+    <row r="240" spans="17:43" x14ac:dyDescent="0.2">
       <c r="Q240" s="17"/>
-      <c r="W240" s="17"/>
-      <c r="Y240" s="65"/>
-      <c r="Z240" s="66" t="s">
+      <c r="AF240" s="80">
+        <v>1395</v>
+      </c>
+      <c r="AG240" s="124">
+        <v>45904</v>
+      </c>
+      <c r="AH240" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI240" s="122"/>
+      <c r="AJ240" s="52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="241" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q241" s="17"/>
+      <c r="W241" s="17"/>
+      <c r="AD241" s="17"/>
+      <c r="AE241" s="43"/>
+      <c r="AF241" s="80">
+        <v>51300</v>
+      </c>
+      <c r="AG241" s="124">
+        <v>45904</v>
+      </c>
+      <c r="AH241" s="52">
+        <v>90</v>
+      </c>
+      <c r="AI241" s="122"/>
+      <c r="AJ241" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP241" s="15"/>
+    </row>
+    <row r="242" spans="17:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q242" s="17"/>
+      <c r="Z242" t="s">
+        <v>223</v>
+      </c>
+      <c r="AF242" s="80">
+        <v>307760</v>
+      </c>
+      <c r="AG242" s="124">
+        <v>43313</v>
+      </c>
+      <c r="AH242" s="52">
+        <v>540</v>
+      </c>
+      <c r="AI242" s="122"/>
+      <c r="AJ242" s="52" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q243" s="17"/>
+      <c r="W243" s="17"/>
+      <c r="Y243" s="65"/>
+      <c r="Z243" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="AA240" s="66"/>
-      <c r="AB240" s="67" t="s">
+      <c r="AA243" s="66"/>
+      <c r="AB243" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="AC240" s="65"/>
-      <c r="AD240" s="67"/>
-      <c r="AF240" s="80">
+      <c r="AC243" s="65"/>
+      <c r="AD243" s="67"/>
+      <c r="AF243" s="80">
         <v>4561</v>
       </c>
-      <c r="AG240" s="125">
+      <c r="AG243" s="124">
         <v>41487</v>
       </c>
-      <c r="AH240" s="52" t="s">
+      <c r="AH243" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="AI240" s="52"/>
-      <c r="AJ240" s="52" t="s">
+      <c r="AI243" s="52"/>
+      <c r="AJ243" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AP240" s="43"/>
-      <c r="AR240" s="43"/>
-    </row>
-    <row r="241" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Q241" s="17"/>
-      <c r="Y241" s="68"/>
-      <c r="Z241" s="69">
+      <c r="AP243" s="43"/>
+      <c r="AR243" s="43"/>
+    </row>
+    <row r="244" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q244" s="17"/>
+      <c r="Y244" s="68"/>
+      <c r="Z244" s="69">
         <f>X84-R84</f>
         <v>72</v>
       </c>
-      <c r="AA241" s="69"/>
-      <c r="AB241" s="70">
+      <c r="AA244" s="69"/>
+      <c r="AB244" s="70">
         <v>72</v>
       </c>
-      <c r="AC241" s="97">
+      <c r="AC244" s="97">
         <v>73</v>
       </c>
-      <c r="AD241" s="98">
+      <c r="AD244" s="98">
         <v>73</v>
       </c>
-      <c r="AF241" s="80">
+      <c r="AF244" s="80">
         <v>585970</v>
       </c>
-      <c r="AG241" s="125">
+      <c r="AG244" s="124">
         <v>45873</v>
       </c>
-      <c r="AH241" s="52">
+      <c r="AH244" s="52">
         <v>1000</v>
       </c>
-      <c r="AI241" s="123"/>
-      <c r="AJ241" s="52" t="s">
+      <c r="AI244" s="122"/>
+      <c r="AJ244" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AP241" s="43"/>
-    </row>
-    <row r="242" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Q242" s="19"/>
-      <c r="Y242" s="68" t="s">
+      <c r="AP244" s="43"/>
+    </row>
+    <row r="245" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Q245" s="19"/>
+      <c r="Y245" s="68" t="s">
         <v>244</v>
       </c>
-      <c r="Z242" s="71">
+      <c r="Z245" s="71">
         <v>1496.23</v>
       </c>
-      <c r="AA242" s="71"/>
-      <c r="AB242" s="72">
+      <c r="AA245" s="71"/>
+      <c r="AB245" s="72">
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC242" s="68">
+      <c r="AC245" s="68">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AD242" s="72">
+      <c r="AD245" s="72">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
-      <c r="AE242" s="17"/>
-      <c r="AF242" s="80">
+      <c r="AE245" s="17"/>
+      <c r="AF245" s="80">
         <v>110000</v>
       </c>
-      <c r="AG242" s="125">
+      <c r="AG245" s="124">
         <v>45866</v>
       </c>
-      <c r="AH242" s="52" t="s">
+      <c r="AH245" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="AI242" s="123"/>
-      <c r="AJ242" s="52" t="s">
+      <c r="AI245" s="122"/>
+      <c r="AJ245" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AP242" s="43"/>
-    </row>
-    <row r="243" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y243" s="68" t="s">
+      <c r="AP245" s="43"/>
+    </row>
+    <row r="246" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Y246" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="Z243" s="69">
-        <f>Z241*Z242</f>
+      <c r="Z246" s="69">
+        <f>Z244*Z245</f>
         <v>107728.56</v>
       </c>
-      <c r="AA243" s="69"/>
-      <c r="AB243" s="70">
-        <f>AB241*AB242</f>
+      <c r="AA246" s="69"/>
+      <c r="AB246" s="70">
+        <f>AB244*AB245</f>
         <v>107784.288</v>
       </c>
-      <c r="AC243" s="97">
-        <f>AC241*AC242</f>
+      <c r="AC246" s="97">
+        <f>AC244*AC245</f>
         <v>73151.183000000005</v>
       </c>
-      <c r="AD243" s="98">
-        <f>AD241*AD242</f>
+      <c r="AD246" s="98">
+        <f>AD244*AD245</f>
         <v>145457.68299999999</v>
       </c>
-      <c r="AE243" s="17"/>
-      <c r="AF243" s="80">
+      <c r="AE246" s="17"/>
+      <c r="AF246" s="80">
         <v>150000</v>
       </c>
-      <c r="AG243" s="125">
+      <c r="AG246" s="124">
         <v>45856</v>
       </c>
-      <c r="AH243" s="52">
+      <c r="AH246" s="52">
         <v>270</v>
       </c>
-      <c r="AI243" s="123"/>
-      <c r="AJ243" s="52" t="s">
+      <c r="AI246" s="122"/>
+      <c r="AJ246" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="244" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y244" s="68" t="s">
+    <row r="247" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Y247" s="68" t="s">
         <v>283</v>
       </c>
-      <c r="Z244" s="71">
+      <c r="Z247" s="71">
         <v>0.36</v>
       </c>
-      <c r="AA244" s="71"/>
-      <c r="AB244" s="72">
+      <c r="AA247" s="71"/>
+      <c r="AB247" s="72">
         <v>0.36</v>
       </c>
-      <c r="AC244" s="68">
+      <c r="AC247" s="68">
         <v>0.36</v>
       </c>
-      <c r="AD244" s="72">
+      <c r="AD247" s="72">
         <v>0.36</v>
       </c>
-      <c r="AF244" s="80">
+      <c r="AF247" s="80">
         <v>150000</v>
       </c>
-      <c r="AG244" s="125">
+      <c r="AG247" s="124">
         <v>45854</v>
       </c>
-      <c r="AH244" s="52">
+      <c r="AH247" s="52">
         <v>270</v>
       </c>
-      <c r="AI244" s="123"/>
-      <c r="AJ244" s="52" t="s">
+      <c r="AI247" s="122"/>
+      <c r="AJ247" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="245" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y245" s="68" t="s">
+    <row r="248" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Y248" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="Z245" s="92">
-        <f>Z243*Z244</f>
+      <c r="Z248" s="92">
+        <f>Z246*Z247</f>
         <v>38782.281599999995</v>
       </c>
-      <c r="AA245" s="92"/>
-      <c r="AB245" s="93">
-        <f>AB243*AB244</f>
+      <c r="AA248" s="92"/>
+      <c r="AB248" s="93">
+        <f>AB246*AB247</f>
         <v>38802.343679999998</v>
       </c>
-      <c r="AC245" s="99">
-        <f>AC244*AC243</f>
+      <c r="AC248" s="99">
+        <f>AC247*AC246</f>
         <v>26334.425879999999</v>
       </c>
-      <c r="AD245" s="100">
-        <f>AD244*AD243</f>
+      <c r="AD248" s="100">
+        <f>AD247*AD246</f>
         <v>52364.765879999992</v>
       </c>
-      <c r="AF245" s="80">
+      <c r="AF248" s="80">
         <v>1665</v>
       </c>
-      <c r="AG245" s="125">
+      <c r="AG248" s="124">
         <v>45832</v>
       </c>
-      <c r="AH245" s="52" t="s">
+      <c r="AH248" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="AI245" s="123"/>
-      <c r="AJ245" s="52" t="s">
+      <c r="AI248" s="122"/>
+      <c r="AJ248" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y246" s="68"/>
-      <c r="Z246" s="71"/>
-      <c r="AA246" s="71"/>
-      <c r="AB246" s="72"/>
-      <c r="AC246" s="68"/>
-      <c r="AD246" s="72"/>
-      <c r="AF246" s="80">
-        <v>324000</v>
-      </c>
-      <c r="AG246" s="125">
-        <v>45831</v>
-      </c>
-      <c r="AH246" s="52">
-        <v>500</v>
-      </c>
-      <c r="AI246" s="123"/>
-      <c r="AJ246" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="247" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y247" s="68" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z247" s="71"/>
-      <c r="AA247" s="71"/>
-      <c r="AB247" s="72"/>
-      <c r="AC247" s="68"/>
-      <c r="AD247" s="72"/>
-      <c r="AF247" s="80">
-        <v>324000</v>
-      </c>
-      <c r="AG247" s="125">
-        <v>45818</v>
-      </c>
-      <c r="AH247" s="52">
-        <v>500</v>
-      </c>
-      <c r="AI247" s="123"/>
-      <c r="AJ247" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="248" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y248" s="68"/>
-      <c r="Z248" s="69"/>
-      <c r="AA248" s="69"/>
-      <c r="AB248" s="72"/>
-      <c r="AC248" s="68"/>
-      <c r="AD248" s="72"/>
-      <c r="AF248" s="80">
-        <v>31780</v>
-      </c>
-      <c r="AG248" s="125">
-        <v>45810</v>
-      </c>
-      <c r="AH248" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI248" s="52"/>
-      <c r="AJ248" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="249" spans="17:42" x14ac:dyDescent="0.2">
+    <row r="249" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y249" s="68"/>
-      <c r="Z249" s="95" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA249" s="95"/>
-      <c r="AB249" s="93">
-        <f>AB245+Z245</f>
-        <v>77584.625279999993</v>
-      </c>
-      <c r="AC249" s="68" t="s">
-        <v>308</v>
-      </c>
-      <c r="AD249" s="100">
-        <f>AC245+AD245</f>
-        <v>78699.191759999987</v>
-      </c>
+      <c r="Z249" s="71"/>
+      <c r="AA249" s="71"/>
+      <c r="AB249" s="72"/>
+      <c r="AC249" s="68"/>
+      <c r="AD249" s="72"/>
       <c r="AF249" s="80">
         <v>324000</v>
       </c>
-      <c r="AG249" s="125">
-        <v>45807</v>
+      <c r="AG249" s="124">
+        <v>45831</v>
       </c>
       <c r="AH249" s="52">
         <v>500</v>
       </c>
-      <c r="AI249" s="52"/>
+      <c r="AI249" s="122"/>
       <c r="AJ249" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="250" spans="17:42" x14ac:dyDescent="0.2">
-      <c r="Y250" s="68"/>
+    <row r="250" spans="17:44" x14ac:dyDescent="0.2">
+      <c r="Y250" s="68" t="s">
+        <v>274</v>
+      </c>
       <c r="Z250" s="71"/>
       <c r="AA250" s="71"/>
       <c r="AB250" s="72"/>
-      <c r="AC250" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD250" s="70">
-        <f>AB260</f>
-        <v>11456.374720000007</v>
-      </c>
+      <c r="AC250" s="68"/>
+      <c r="AD250" s="72"/>
       <c r="AF250" s="80">
-        <v>325000</v>
-      </c>
-      <c r="AG250" s="125">
-        <v>45806</v>
+        <v>324000</v>
+      </c>
+      <c r="AG250" s="124">
+        <v>45818</v>
       </c>
       <c r="AH250" s="52">
         <v>500</v>
       </c>
-      <c r="AI250" s="52"/>
+      <c r="AI250" s="122"/>
       <c r="AJ250" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="251" spans="17:42" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="251" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y251" s="68"/>
-      <c r="Z251" s="71" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA251" s="71"/>
-      <c r="AB251" s="70">
-        <v>15300</v>
-      </c>
+      <c r="Z251" s="69"/>
+      <c r="AA251" s="69"/>
+      <c r="AB251" s="72"/>
       <c r="AC251" s="68"/>
       <c r="AD251" s="72"/>
       <c r="AF251" s="80">
-        <v>648000</v>
-      </c>
-      <c r="AG251" s="125">
-        <v>45786</v>
-      </c>
-      <c r="AH251" s="52">
-        <v>1000</v>
-      </c>
-      <c r="AI251" s="52" t="s">
-        <v>129</v>
-      </c>
+        <v>31780</v>
+      </c>
+      <c r="AG251" s="124">
+        <v>45810</v>
+      </c>
+      <c r="AH251" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="AI251" s="52"/>
       <c r="AJ251" s="52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="252" spans="17:42" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="252" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y252" s="68"/>
-      <c r="Z252" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="AA252" s="75"/>
-      <c r="AB252" s="70">
-        <v>1200</v>
+      <c r="Z252" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA252" s="95"/>
+      <c r="AB252" s="93">
+        <f>AB248+Z248</f>
+        <v>77584.625279999993</v>
       </c>
       <c r="AC252" s="68" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AD252" s="100">
-        <f>AD249-AD250</f>
-        <v>67242.81703999998</v>
+        <f>AC248+AD248</f>
+        <v>78699.191759999987</v>
       </c>
       <c r="AF252" s="80">
-        <v>514200</v>
-      </c>
-      <c r="AG252" s="125">
-        <v>45772</v>
+        <v>324000</v>
+      </c>
+      <c r="AG252" s="124">
+        <v>45807</v>
       </c>
       <c r="AH252" s="52">
-        <v>800</v>
-      </c>
-      <c r="AI252" s="52" t="s">
-        <v>127</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="AI252" s="52"/>
       <c r="AJ252" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="17:42" x14ac:dyDescent="0.2">
+    <row r="253" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y253" s="68"/>
-      <c r="Z253" s="75" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA253" s="75"/>
-      <c r="AB253" s="70">
-        <v>12900</v>
-      </c>
+      <c r="Z253" s="71"/>
+      <c r="AA253" s="71"/>
+      <c r="AB253" s="72"/>
       <c r="AC253" s="68" t="s">
-        <v>341</v>
-      </c>
-      <c r="AD253" s="100">
-        <v>50000</v>
+        <v>68</v>
+      </c>
+      <c r="AD253" s="70">
+        <f>AB263</f>
+        <v>11456.374720000007</v>
       </c>
       <c r="AF253" s="80">
         <v>325000</v>
       </c>
-      <c r="AG253" s="125">
-        <v>45762</v>
+      <c r="AG253" s="124">
+        <v>45806</v>
       </c>
       <c r="AH253" s="52">
         <v>500</v>
@@ -18982,106 +20130,117 @@
         <v>99</v>
       </c>
     </row>
-    <row r="254" spans="17:42" x14ac:dyDescent="0.2">
+    <row r="254" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y254" s="68"/>
-      <c r="Z254" s="75" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA254" s="75"/>
+      <c r="Z254" s="71" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA254" s="71"/>
       <c r="AB254" s="70">
-        <v>7000</v>
-      </c>
-      <c r="AC254" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="AD254" s="100">
-        <f>AD252-AD253</f>
-        <v>17242.81703999998</v>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="AC254" s="68"/>
+      <c r="AD254" s="72"/>
       <c r="AF254" s="80">
-        <v>632000</v>
-      </c>
-      <c r="AG254" s="125">
-        <v>45749</v>
+        <v>648000</v>
+      </c>
+      <c r="AG254" s="124">
+        <v>45786</v>
       </c>
       <c r="AH254" s="52">
         <v>1000</v>
       </c>
-      <c r="AI254" s="52"/>
+      <c r="AI254" s="52" t="s">
+        <v>129</v>
+      </c>
       <c r="AJ254" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="255" spans="17:42" x14ac:dyDescent="0.2">
+    <row r="255" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y255" s="68"/>
       <c r="Z255" s="75" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AA255" s="75"/>
       <c r="AB255" s="70">
-        <v>5000</v>
-      </c>
-      <c r="AC255" s="68"/>
-      <c r="AD255" s="72" t="s">
-        <v>194</v>
+        <v>1200</v>
+      </c>
+      <c r="AC255" s="68" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD255" s="100">
+        <f>AD252-AD253</f>
+        <v>67242.81703999998</v>
       </c>
       <c r="AF255" s="80">
-        <v>632000</v>
-      </c>
-      <c r="AG255" s="125">
-        <v>45736</v>
+        <v>514200</v>
+      </c>
+      <c r="AG255" s="124">
+        <v>45772</v>
       </c>
       <c r="AH255" s="52">
-        <v>1000</v>
-      </c>
-      <c r="AI255" s="52"/>
+        <v>800</v>
+      </c>
+      <c r="AI255" s="52" t="s">
+        <v>127</v>
+      </c>
       <c r="AJ255" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="256" spans="17:42" x14ac:dyDescent="0.2">
+    <row r="256" spans="17:44" x14ac:dyDescent="0.2">
       <c r="Y256" s="68"/>
       <c r="Z256" s="75" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AA256" s="75"/>
-      <c r="AB256" s="94">
-        <v>10400</v>
-      </c>
-      <c r="AC256" s="68"/>
-      <c r="AD256" s="72"/>
+      <c r="AB256" s="70">
+        <v>12900</v>
+      </c>
+      <c r="AC256" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="AD256" s="100">
+        <v>50000</v>
+      </c>
       <c r="AF256" s="80">
-        <v>632000</v>
-      </c>
-      <c r="AG256" s="125">
-        <v>45721</v>
+        <v>325000</v>
+      </c>
+      <c r="AG256" s="124">
+        <v>45762</v>
       </c>
       <c r="AH256" s="52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI256" s="52"/>
       <c r="AJ256" s="52" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
     </row>
     <row r="257" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y257" s="68"/>
       <c r="Z257" s="75" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AA257" s="75"/>
-      <c r="AB257" s="94">
-        <v>5441</v>
-      </c>
-      <c r="AC257" s="68"/>
-      <c r="AD257" s="72"/>
+      <c r="AB257" s="70">
+        <v>7000</v>
+      </c>
+      <c r="AC257" s="68" t="s">
+        <v>341</v>
+      </c>
+      <c r="AD257" s="100">
+        <f>AD255-AD256</f>
+        <v>17242.81703999998</v>
+      </c>
       <c r="AF257" s="80">
         <v>632000</v>
       </c>
-      <c r="AG257" s="126">
-        <v>45706</v>
-      </c>
-      <c r="AH257" s="127">
+      <c r="AG257" s="124">
+        <v>45749</v>
+      </c>
+      <c r="AH257" s="52">
         <v>1000</v>
       </c>
       <c r="AI257" s="52"/>
@@ -19091,23 +20250,26 @@
     </row>
     <row r="258" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y258" s="68"/>
-      <c r="Z258" s="95" t="s">
-        <v>307</v>
-      </c>
-      <c r="AA258" s="95"/>
-      <c r="AB258" s="93">
-        <f>AB249-AB251+AB252-AB253-AB254+AB255+AB256-AB257</f>
-        <v>53543.625279999993</v>
+      <c r="Z258" s="75" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA258" s="75"/>
+      <c r="AB258" s="70">
+        <v>5000</v>
       </c>
       <c r="AC258" s="68"/>
-      <c r="AD258" s="72"/>
+      <c r="AD258" s="72" t="s">
+        <v>194</v>
+      </c>
       <c r="AF258" s="80">
-        <v>21610</v>
-      </c>
-      <c r="AG258" s="126">
-        <v>45692</v>
-      </c>
-      <c r="AH258" s="52"/>
+        <v>632000</v>
+      </c>
+      <c r="AG258" s="124">
+        <v>45736</v>
+      </c>
+      <c r="AH258" s="52">
+        <v>1000</v>
+      </c>
       <c r="AI258" s="52"/>
       <c r="AJ258" s="52" t="s">
         <v>16</v>
@@ -19115,23 +20277,23 @@
     </row>
     <row r="259" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y259" s="68"/>
-      <c r="Z259" s="95" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA259" s="95"/>
-      <c r="AB259" s="93">
-        <v>65000</v>
+      <c r="Z259" s="75" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA259" s="75"/>
+      <c r="AB259" s="94">
+        <v>10400</v>
       </c>
       <c r="AC259" s="68"/>
       <c r="AD259" s="72"/>
       <c r="AF259" s="80">
-        <v>200000</v>
-      </c>
-      <c r="AG259" s="126">
-        <v>45687</v>
-      </c>
-      <c r="AH259" s="127">
-        <v>300</v>
+        <v>632000</v>
+      </c>
+      <c r="AG259" s="124">
+        <v>45721</v>
+      </c>
+      <c r="AH259" s="52">
+        <v>1000</v>
       </c>
       <c r="AI259" s="52"/>
       <c r="AJ259" s="52" t="s">
@@ -19141,68 +20303,71 @@
     <row r="260" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y260" s="68"/>
       <c r="Z260" s="75" t="s">
-        <v>68</v>
+        <v>282</v>
       </c>
       <c r="AA260" s="75"/>
-      <c r="AB260" s="102">
-        <f>AB259-AB258</f>
-        <v>11456.374720000007</v>
+      <c r="AB260" s="94">
+        <v>5441</v>
       </c>
       <c r="AC260" s="68"/>
       <c r="AD260" s="72"/>
       <c r="AF260" s="80">
-        <v>50000</v>
-      </c>
-      <c r="AG260" s="126">
-        <v>45680</v>
-      </c>
-      <c r="AH260" s="115"/>
+        <v>632000</v>
+      </c>
+      <c r="AG260" s="125">
+        <v>45706</v>
+      </c>
+      <c r="AH260" s="126">
+        <v>1000</v>
+      </c>
       <c r="AI260" s="52"/>
       <c r="AJ260" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="261" spans="18:36" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="R261" s="77"/>
-      <c r="S261" s="78"/>
-      <c r="T261" s="77"/>
-      <c r="U261" s="77"/>
-      <c r="Y261" s="73"/>
-      <c r="Z261" s="76"/>
-      <c r="AA261" s="76"/>
-      <c r="AB261" s="74"/>
-      <c r="AC261" s="73"/>
-      <c r="AD261" s="101"/>
+    <row r="261" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="Y261" s="68"/>
+      <c r="Z261" s="95" t="s">
+        <v>307</v>
+      </c>
+      <c r="AA261" s="95"/>
+      <c r="AB261" s="93">
+        <f>AB252-AB254+AB255-AB256-AB257+AB258+AB259-AB260</f>
+        <v>53543.625279999993</v>
+      </c>
+      <c r="AC261" s="68"/>
+      <c r="AD261" s="72"/>
       <c r="AF261" s="80">
-        <v>300000</v>
-      </c>
-      <c r="AG261" s="126">
-        <v>45674</v>
-      </c>
-      <c r="AH261" s="128">
-        <v>500</v>
-      </c>
+        <v>21610</v>
+      </c>
+      <c r="AG261" s="125">
+        <v>45692</v>
+      </c>
+      <c r="AH261" s="52"/>
       <c r="AI261" s="52"/>
       <c r="AJ261" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="262" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R262" s="79"/>
-      <c r="S262" s="79"/>
-      <c r="T262" s="79"/>
-      <c r="U262" s="79"/>
-      <c r="Z262" s="75"/>
-      <c r="AA262" s="75"/>
-      <c r="AB262" s="17"/>
+      <c r="Y262" s="68"/>
+      <c r="Z262" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA262" s="95"/>
+      <c r="AB262" s="93">
+        <v>65000</v>
+      </c>
+      <c r="AC262" s="68"/>
+      <c r="AD262" s="72"/>
       <c r="AF262" s="80">
-        <v>332000</v>
-      </c>
-      <c r="AG262" s="126">
-        <v>45664</v>
-      </c>
-      <c r="AH262" s="128">
-        <v>500</v>
+        <v>200000</v>
+      </c>
+      <c r="AG262" s="125">
+        <v>45687</v>
+      </c>
+      <c r="AH262" s="126">
+        <v>300</v>
       </c>
       <c r="AI262" s="52"/>
       <c r="AJ262" s="52" t="s">
@@ -19210,47 +20375,47 @@
       </c>
     </row>
     <row r="263" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R263" s="79"/>
-      <c r="S263" s="79"/>
-      <c r="T263" s="79"/>
-      <c r="U263" s="79"/>
+      <c r="Y263" s="68"/>
+      <c r="Z263" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA263" s="75"/>
+      <c r="AB263" s="102">
+        <f>AB262-AB261</f>
+        <v>11456.374720000007</v>
+      </c>
+      <c r="AC263" s="68"/>
+      <c r="AD263" s="72"/>
       <c r="AF263" s="80">
-        <v>332000</v>
-      </c>
-      <c r="AG263" s="126">
-        <v>45656</v>
-      </c>
-      <c r="AH263" s="128">
-        <v>500</v>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="AG263" s="125">
+        <v>45680</v>
+      </c>
+      <c r="AH263" s="114"/>
       <c r="AI263" s="52"/>
       <c r="AJ263" s="52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R264" s="43"/>
-      <c r="T264" s="43"/>
-      <c r="U264" s="43"/>
-      <c r="Y264" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z264" s="17">
-        <f>SUM(AC87)</f>
-        <v>1107210.2</v>
-      </c>
-      <c r="AA264" s="17"/>
-      <c r="AB264" s="17">
-        <f>AC88+AC89+AC90</f>
-        <v>1107782.96</v>
-      </c>
+    <row r="264" spans="18:36" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R264" s="77"/>
+      <c r="S264" s="78"/>
+      <c r="T264" s="77"/>
+      <c r="U264" s="77"/>
+      <c r="Y264" s="73"/>
+      <c r="Z264" s="76"/>
+      <c r="AA264" s="76"/>
+      <c r="AB264" s="74"/>
+      <c r="AC264" s="73"/>
+      <c r="AD264" s="101"/>
       <c r="AF264" s="80">
-        <v>339500</v>
-      </c>
-      <c r="AG264" s="126">
-        <v>45649</v>
-      </c>
-      <c r="AH264" s="128">
+        <v>300000</v>
+      </c>
+      <c r="AG264" s="125">
+        <v>45674</v>
+      </c>
+      <c r="AH264" s="127">
         <v>500</v>
       </c>
       <c r="AI264" s="52"/>
@@ -19259,26 +20424,21 @@
       </c>
     </row>
     <row r="265" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y265" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z265" s="15">
-        <f>72*O87</f>
-        <v>107728.56</v>
-      </c>
-      <c r="AA265" s="15"/>
-      <c r="AB265" s="17">
-        <f>72*O91</f>
-        <v>107784.288</v>
-      </c>
+      <c r="R265" s="79"/>
+      <c r="S265" s="79"/>
+      <c r="T265" s="79"/>
+      <c r="U265" s="79"/>
+      <c r="Z265" s="75"/>
+      <c r="AA265" s="75"/>
+      <c r="AB265" s="17"/>
       <c r="AF265" s="80">
-        <v>679000</v>
+        <v>332000</v>
       </c>
       <c r="AG265" s="125">
-        <v>45643</v>
-      </c>
-      <c r="AH265" s="52">
-        <v>1000</v>
+        <v>45664</v>
+      </c>
+      <c r="AH265" s="127">
+        <v>500</v>
       </c>
       <c r="AI265" s="52"/>
       <c r="AJ265" s="52" t="s">
@@ -19286,600 +20446,625 @@
       </c>
     </row>
     <row r="266" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y266" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z266" s="43">
-        <f>Z265*0.25</f>
-        <v>26932.14</v>
-      </c>
-      <c r="AA266" s="43"/>
-      <c r="AB266" s="17">
-        <f>AB265*0.25</f>
-        <v>26946.072</v>
+      <c r="R266" s="79"/>
+      <c r="S266" s="79"/>
+      <c r="T266" s="79"/>
+      <c r="U266" s="79"/>
+      <c r="AF266" s="80">
+        <v>332000</v>
+      </c>
+      <c r="AG266" s="125">
+        <v>45656</v>
+      </c>
+      <c r="AH266" s="127">
+        <v>500</v>
+      </c>
+      <c r="AI266" s="52"/>
+      <c r="AJ266" s="52" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="267" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="R267" s="43"/>
+      <c r="T267" s="43"/>
+      <c r="U267" s="43"/>
       <c r="Y267" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z267">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="AB267" s="91">
-        <v>18.309999999999999</v>
+        <v>209</v>
+      </c>
+      <c r="Z267" s="17">
+        <f>SUM(AC87)</f>
+        <v>1107210.2</v>
+      </c>
+      <c r="AA267" s="17"/>
+      <c r="AB267" s="17">
+        <f>AC88+AC89+AC90</f>
+        <v>1107782.96</v>
+      </c>
+      <c r="AF267" s="80">
+        <v>339500</v>
+      </c>
+      <c r="AG267" s="125">
+        <v>45649</v>
+      </c>
+      <c r="AH267" s="127">
+        <v>500</v>
+      </c>
+      <c r="AI267" s="52"/>
+      <c r="AJ267" s="52" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="268" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y268" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z268" s="43">
-        <f>Z266*Z267</f>
-        <v>509017.44599999994</v>
-      </c>
-      <c r="AA268" s="43"/>
+        <v>211</v>
+      </c>
+      <c r="Z268" s="15">
+        <f>72*O87</f>
+        <v>107728.56</v>
+      </c>
+      <c r="AA268" s="15"/>
       <c r="AB268" s="17">
-        <v>491765.81</v>
-      </c>
-      <c r="AD268" s="88" t="s">
-        <v>237</v>
-      </c>
-      <c r="AE268" s="88"/>
-      <c r="AF268" s="88"/>
-      <c r="AG268" s="88"/>
-      <c r="AH268" s="88"/>
+        <f>72*O91</f>
+        <v>107784.288</v>
+      </c>
+      <c r="AF268" s="80">
+        <v>679000</v>
+      </c>
+      <c r="AG268" s="124">
+        <v>45643</v>
+      </c>
+      <c r="AH268" s="52">
+        <v>1000</v>
+      </c>
+      <c r="AI268" s="52"/>
+      <c r="AJ268" s="52" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="269" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y269" s="41" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Z269" s="43">
-        <f>Z268*0.05</f>
-        <v>25450.872299999999</v>
+        <f>Z268*0.25</f>
+        <v>26932.14</v>
       </c>
       <c r="AA269" s="43"/>
       <c r="AB269" s="17">
-        <f>AB268*0.05</f>
-        <v>24588.290500000003</v>
-      </c>
-      <c r="AD269" s="52"/>
-      <c r="AE269" s="85" t="s">
-        <v>236</v>
-      </c>
-      <c r="AF269" s="85" t="s">
-        <v>234</v>
-      </c>
-      <c r="AG269" s="82"/>
-      <c r="AH269" s="82" t="s">
-        <v>235</v>
+        <f>AB268*0.25</f>
+        <v>26946.072</v>
       </c>
     </row>
     <row r="270" spans="18:36" x14ac:dyDescent="0.2">
       <c r="Y270" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z270">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AB270" s="91">
+        <v>18.309999999999999</v>
+      </c>
+    </row>
+    <row r="271" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="Y271" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z271" s="43">
+        <f>Z269*Z270</f>
+        <v>509017.44599999994</v>
+      </c>
+      <c r="AA271" s="43"/>
+      <c r="AB271" s="17">
+        <v>491765.81</v>
+      </c>
+      <c r="AD271" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="AE271" s="88"/>
+      <c r="AF271" s="88"/>
+      <c r="AG271" s="88"/>
+      <c r="AH271" s="88"/>
+    </row>
+    <row r="272" spans="18:36" x14ac:dyDescent="0.2">
+      <c r="Y272" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z272" s="43">
+        <f>Z271*0.05</f>
+        <v>25450.872299999999</v>
+      </c>
+      <c r="AA272" s="43"/>
+      <c r="AB272" s="17">
+        <f>AB271*0.05</f>
+        <v>24588.290500000003</v>
+      </c>
+      <c r="AD272" s="52"/>
+      <c r="AE272" s="85" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF272" s="85" t="s">
+        <v>234</v>
+      </c>
+      <c r="AG272" s="82"/>
+      <c r="AH272" s="82" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="273" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y273" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z270" s="110">
+      <c r="Z273" s="110">
         <f>O87</f>
         <v>1496.23</v>
       </c>
-      <c r="AA270" s="110"/>
-      <c r="AB270" s="110">
+      <c r="AA273" s="110"/>
+      <c r="AB273" s="110">
         <f>O91</f>
         <v>1497.0039999999999</v>
       </c>
-      <c r="AC270" s="111"/>
-      <c r="AD270" s="52" t="s">
+      <c r="AC273" s="111"/>
+      <c r="AD273" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AE270" s="53">
+      <c r="AE273" s="53">
         <f>SUM(W66,W76,W87,W91,W101,W122)</f>
         <v>8571607.8409999982</v>
       </c>
-      <c r="AF270" s="86">
-        <f>SUMIF(AJ220:AJ265,"Arauco",AF220:AF265)</f>
+      <c r="AF273" s="86">
+        <f>SUMIF(AJ223:AJ268,"Arauco",AF223:AF268)</f>
         <v>8589229</v>
       </c>
-      <c r="AG270" s="52" t="s">
+      <c r="AG273" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="AH270" s="87">
-        <f>AE270-AF270</f>
+      <c r="AH273" s="87">
+        <f>AE273-AF273</f>
         <v>-17621.159000001848</v>
       </c>
     </row>
-    <row r="271" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="X271" s="111"/>
-      <c r="Y271" s="41" t="s">
+    <row r="274" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="X274" s="111"/>
+      <c r="Y274" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Z271" s="105">
-        <f>Z268-Z269</f>
+      <c r="Z274" s="105">
+        <f>Z271-Z272</f>
         <v>483566.57369999995</v>
       </c>
-      <c r="AA271" s="105"/>
-      <c r="AB271" s="104">
-        <f>AB268-AB269</f>
+      <c r="AA274" s="105"/>
+      <c r="AB274" s="104">
+        <f>AB271-AB272</f>
         <v>467177.51949999999</v>
       </c>
-      <c r="AD271" s="52" t="s">
+      <c r="AD274" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="AE271" s="53">
-        <f>SUM(W83,W98,W109,W116,W118,W131,W143,W146,W153,W161,W169,W176,W183,W193)</f>
-        <v>4396186.335</v>
-      </c>
-      <c r="AF271" s="86">
-        <f>SUMIF(AJ219:AJ265,"CPP",AF219:AF265)</f>
-        <v>4326001</v>
-      </c>
-      <c r="AG271" s="52" t="s">
+      <c r="AE274" s="53">
+        <f>SUM(W83,W98,W109,W116,W118,W131,W143,W146,W153,W161,W169,W176,W183,W193,W206)</f>
+        <v>4994869.585</v>
+      </c>
+      <c r="AF274" s="86">
+        <f>SUMIF(AJ222:AJ268,"CPP",AF222:AF268)</f>
+        <v>4920001</v>
+      </c>
+      <c r="AG274" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AH271" s="87">
-        <f>AE271-AF271</f>
-        <v>70185.334999999963</v>
-      </c>
-    </row>
-    <row r="272" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="Y272" s="41"/>
-      <c r="Z272" t="s">
+      <c r="AH274" s="87">
+        <f>AE274-AF274</f>
+        <v>74868.584999999963</v>
+      </c>
+    </row>
+    <row r="275" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y275" s="41"/>
+      <c r="Z275" t="s">
         <v>136</v>
       </c>
-      <c r="AB272" t="s">
+      <c r="AB275" t="s">
         <v>136</v>
       </c>
-      <c r="AD272" s="52" t="s">
+      <c r="AD275" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="AE272" s="53">
-        <f>SUM(AE270:AE271)</f>
-        <v>12967794.175999999</v>
-      </c>
-      <c r="AF272" s="86">
-        <f>SUM(AF225:AF265)</f>
+      <c r="AE275" s="53">
+        <f>SUM(AE273:AE274)</f>
+        <v>13566477.425999999</v>
+      </c>
+      <c r="AF275" s="86">
+        <f>SUM(AF228:AF268)</f>
         <v>12180230</v>
       </c>
-      <c r="AG272" s="52" t="s">
+      <c r="AG275" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="AH272" s="87">
-        <f>SUM(AH270:AH271)</f>
-        <v>52564.175999998115</v>
-      </c>
-    </row>
-    <row r="273" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y273" s="41" t="s">
+      <c r="AH275" s="87">
+        <f>SUM(AH273:AH274)</f>
+        <v>57247.425999998115</v>
+      </c>
+    </row>
+    <row r="276" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y276" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="Z273" s="17">
+      <c r="Z276" s="17">
         <f>AC101</f>
         <v>711470.40999999992</v>
       </c>
-      <c r="AA273" s="17"/>
-      <c r="AB273" s="17">
+      <c r="AA276" s="17"/>
+      <c r="AB276" s="17">
         <f>AC122</f>
         <v>1235394.02</v>
       </c>
     </row>
-    <row r="274" spans="24:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y274" s="41" t="s">
+    <row r="277" spans="24:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y277" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="Z274" s="17">
+      <c r="Z277" s="17">
         <f>73*O101</f>
         <v>73151.183000000005</v>
       </c>
-      <c r="AA274" s="17"/>
-      <c r="AB274" s="15">
+      <c r="AA277" s="17"/>
+      <c r="AB277" s="15">
         <f>73*O122</f>
         <v>145457.68299999999</v>
       </c>
-      <c r="AF274" s="56" t="s">
+      <c r="AF277" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="AG274" s="56"/>
-      <c r="AI274" s="57" t="s">
+      <c r="AG277" s="56"/>
+      <c r="AI277" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="AJ274" s="57"/>
-      <c r="AK274" s="57"/>
-      <c r="AL274" s="36"/>
-      <c r="AM274" s="56" t="s">
+      <c r="AJ277" s="57"/>
+      <c r="AK277" s="57"/>
+      <c r="AL277" s="36"/>
+      <c r="AM277" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="AN274" s="56"/>
-    </row>
-    <row r="275" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y275" s="41" t="s">
+      <c r="AN277" s="56"/>
+    </row>
+    <row r="278" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y278" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="Z275" s="17">
-        <f>Z274*0.25</f>
+      <c r="Z278" s="17">
+        <f>Z277*0.25</f>
         <v>18287.795750000001</v>
       </c>
-      <c r="AA275" s="17"/>
-      <c r="AB275" s="43">
-        <f>AB274*0.25</f>
+      <c r="AA278" s="17"/>
+      <c r="AB278" s="43">
+        <f>AB277*0.25</f>
         <v>36364.420749999997</v>
       </c>
-      <c r="AF275" s="41" t="s">
+      <c r="AF278" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="AI275" s="49"/>
-      <c r="AJ275" s="49"/>
-      <c r="AK275" s="49"/>
-      <c r="AM275" s="41" t="s">
+      <c r="AI278" s="49"/>
+      <c r="AJ278" s="49"/>
+      <c r="AK278" s="49"/>
+      <c r="AM278" s="41" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="276" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y276" s="41" t="s">
+    <row r="279" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y279" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="Z276">
+      <c r="Z279">
         <v>18.2</v>
       </c>
-      <c r="AB276" s="91">
+      <c r="AB279" s="91">
         <v>17.7</v>
       </c>
-      <c r="AF276" t="s">
+      <c r="AF279" t="s">
         <v>137</v>
       </c>
-      <c r="AG276">
+      <c r="AG279">
         <v>3300</v>
       </c>
-      <c r="AI276" s="49" t="s">
+      <c r="AI279" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="AJ276" s="49" t="s">
+      <c r="AJ279" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="AK276" s="49" t="s">
+      <c r="AK279" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AM276" t="s">
+      <c r="AM279" t="s">
         <v>137</v>
       </c>
-      <c r="AN276">
+      <c r="AN279">
         <v>3300</v>
       </c>
     </row>
-    <row r="277" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y277" s="41" t="s">
+    <row r="280" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y280" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="Z277" s="17">
-        <f>Z275*Z276</f>
+      <c r="Z280" s="17">
+        <f>Z278*Z279</f>
         <v>332837.88264999999</v>
       </c>
-      <c r="AA277" s="17"/>
-      <c r="AB277" s="43">
-        <f>AB275*AB276</f>
+      <c r="AA280" s="17"/>
+      <c r="AB280" s="43">
+        <f>AB278*AB279</f>
         <v>643650.24727499997</v>
       </c>
-      <c r="AF277" t="s">
+      <c r="AF280" t="s">
         <v>138</v>
       </c>
-      <c r="AG277">
+      <c r="AG280">
         <f>O66</f>
         <v>3370.0310000000004</v>
       </c>
-      <c r="AI277" s="49">
+      <c r="AI280" s="49">
         <v>15</v>
       </c>
-      <c r="AJ277" s="49">
+      <c r="AJ280" s="49">
         <f>AG62</f>
         <v>0</v>
       </c>
-      <c r="AK277" s="50">
-        <f>AI277*AJ277</f>
-        <v>0</v>
-      </c>
-      <c r="AM277" t="s">
+      <c r="AK280" s="50">
+        <f>AI280*AJ280</f>
+        <v>0</v>
+      </c>
+      <c r="AM280" t="s">
         <v>138</v>
       </c>
-      <c r="AN277">
+      <c r="AN280">
         <v>3370.0309999999999</v>
       </c>
     </row>
-    <row r="278" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y278" s="103" t="s">
+    <row r="281" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y281" s="103" t="s">
         <v>213</v>
       </c>
-      <c r="Z278" s="17">
-        <f>Z277*0.05</f>
+      <c r="Z281" s="17">
+        <f>Z280*0.05</f>
         <v>16641.894132500001</v>
       </c>
-      <c r="AA278" s="17"/>
-      <c r="AB278" s="43">
-        <f>AB277*0.05</f>
+      <c r="AA281" s="17"/>
+      <c r="AB281" s="43">
+        <f>AB280*0.05</f>
         <v>32182.51236375</v>
       </c>
-      <c r="AF278" t="s">
+      <c r="AF281" t="s">
         <v>139</v>
       </c>
-      <c r="AG278">
-        <f>AG277-AG276</f>
+      <c r="AG281">
+        <f>AG280-AG279</f>
         <v>70.031000000000404</v>
       </c>
-      <c r="AI278" s="49">
+      <c r="AI281" s="49">
         <v>15</v>
       </c>
-      <c r="AJ278" s="49">
+      <c r="AJ281" s="49">
         <f>AG63</f>
         <v>0</v>
       </c>
-      <c r="AK278" s="50">
-        <f t="shared" ref="AK278:AK280" si="90">AI278*AJ278</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="X279" s="111"/>
-      <c r="Y279" s="41" t="s">
+      <c r="AK281" s="50">
+        <f t="shared" ref="AK281:AK283" si="91">AI281*AJ281</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="X282" s="111"/>
+      <c r="Y282" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="Z279" s="110">
+      <c r="Z282" s="110">
         <f>O101</f>
         <v>1002.071</v>
       </c>
-      <c r="AA279" s="110"/>
-      <c r="AB279" s="110">
+      <c r="AA282" s="110"/>
+      <c r="AB282" s="110">
         <f>O122</f>
         <v>1992.5709999999999</v>
       </c>
-      <c r="AF279" t="s">
+      <c r="AF282" t="s">
         <v>140</v>
       </c>
-      <c r="AG279" s="15">
+      <c r="AG282" s="15">
         <v>755</v>
       </c>
-      <c r="AI279" s="49">
+      <c r="AI282" s="49">
         <v>15</v>
       </c>
-      <c r="AJ279" s="49">
+      <c r="AJ282" s="49">
         <f>AG64</f>
         <v>0</v>
       </c>
-      <c r="AK279" s="50">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="AM279" t="s">
+      <c r="AK282" s="50">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="AM282" t="s">
         <v>136</v>
       </c>
-      <c r="AN279" s="43">
-        <f>SUM(AF258:AF265)</f>
+      <c r="AN282" s="43">
+        <f>SUM(AF261:AF268)</f>
         <v>2254110</v>
       </c>
     </row>
-    <row r="280" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y280" s="41" t="s">
+    <row r="283" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y283" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Z280" s="104">
-        <f>Z277-Z278</f>
+      <c r="Z283" s="104">
+        <f>Z280-Z281</f>
         <v>316195.98851749999</v>
       </c>
-      <c r="AA280" s="104"/>
-      <c r="AB280" s="104">
-        <f>AB277-AB278</f>
+      <c r="AA283" s="104"/>
+      <c r="AB283" s="104">
+        <f>AB280-AB281</f>
         <v>611467.73491124995</v>
       </c>
-      <c r="AF280" t="s">
+      <c r="AF283" t="s">
         <v>159</v>
       </c>
-      <c r="AG280" s="44">
-        <f>AG278*AG279</f>
+      <c r="AG283" s="44">
+        <f>AG281*AG282</f>
         <v>52873.405000000304</v>
       </c>
-      <c r="AI280" s="49">
+      <c r="AI283" s="49">
         <v>15</v>
       </c>
-      <c r="AJ280" s="49">
+      <c r="AJ283" s="49">
         <f>AG65</f>
         <v>0</v>
       </c>
-      <c r="AK280" s="50">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="AM280" t="s">
+      <c r="AK283" s="50">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="AM283" t="s">
         <v>147</v>
       </c>
-      <c r="AN280" s="17">
+      <c r="AN283" s="17">
         <f>W66</f>
         <v>2260662.449</v>
       </c>
     </row>
-    <row r="281" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Z281" t="s">
+    <row r="284" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Z284" t="s">
         <v>136</v>
       </c>
-      <c r="AB281" t="s">
+      <c r="AB284" t="s">
         <v>136</v>
       </c>
-      <c r="AI281" s="49"/>
-      <c r="AJ281" s="49"/>
-      <c r="AK281" s="50"/>
-      <c r="AM281" s="41" t="s">
+      <c r="AI284" s="49"/>
+      <c r="AJ284" s="49"/>
+      <c r="AK284" s="50"/>
+      <c r="AM284" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="AN281" s="45">
-        <f>AN279-AN280</f>
+      <c r="AN284" s="45">
+        <f>AN282-AN283</f>
         <v>-6552.4490000000224</v>
       </c>
     </row>
-    <row r="282" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y282" s="41"/>
-      <c r="AB282" s="111"/>
-      <c r="AF282" t="s">
+    <row r="285" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y285" s="41"/>
+      <c r="AB285" s="111"/>
+      <c r="AF285" t="s">
         <v>145</v>
       </c>
-      <c r="AG282" s="17">
+      <c r="AG285" s="17">
         <v>2491500</v>
       </c>
-      <c r="AI282" s="49"/>
-      <c r="AJ282" s="49" t="s">
+      <c r="AI285" s="49"/>
+      <c r="AJ285" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="AK282" s="50">
-        <f>SUM(AK277:AK280)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y283" s="41"/>
-      <c r="AF283" t="s">
+      <c r="AK285" s="50">
+        <f>SUM(AK280:AK283)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y286" s="41"/>
+      <c r="AF286" t="s">
         <v>141</v>
       </c>
-      <c r="AG283" s="17">
+      <c r="AG286" s="17">
         <f>AC66</f>
         <v>2544373.4050000003</v>
       </c>
-      <c r="AI283" s="49"/>
-      <c r="AJ283" s="49" t="s">
+      <c r="AI286" s="49"/>
+      <c r="AJ286" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="AK283" s="51">
-        <f>AG284</f>
+      <c r="AK286" s="51">
+        <f>AG287</f>
         <v>52873.405000000261</v>
       </c>
     </row>
-    <row r="284" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y284" s="41"/>
-      <c r="AF284" t="s">
+    <row r="287" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y287" s="41"/>
+      <c r="AF287" t="s">
         <v>159</v>
       </c>
-      <c r="AG284" s="44">
-        <f>AG283-AG282</f>
+      <c r="AG287" s="44">
+        <f>AG286-AG285</f>
         <v>52873.405000000261</v>
       </c>
-      <c r="AI284" s="49"/>
-      <c r="AJ284" s="49" t="s">
+      <c r="AI287" s="49"/>
+      <c r="AJ287" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="AK284" s="51">
-        <f>+AK283-AK282</f>
+      <c r="AK287" s="51">
+        <f>+AK286-AK285</f>
         <v>52873.405000000261</v>
       </c>
     </row>
-    <row r="285" spans="24:40" x14ac:dyDescent="0.2">
-      <c r="Y285" s="41"/>
-    </row>
-    <row r="286" spans="24:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y286" s="41"/>
-      <c r="AF286" t="s">
+    <row r="288" spans="24:40" x14ac:dyDescent="0.2">
+      <c r="Y288" s="41"/>
+    </row>
+    <row r="289" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y289" s="41"/>
+      <c r="AF289" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="287" spans="24:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y287" s="103"/>
-      <c r="AB287" s="43"/>
-      <c r="AF287" t="s">
+    <row r="290" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y290" s="103"/>
+      <c r="AB290" s="43"/>
+      <c r="AF290" t="s">
         <v>155</v>
       </c>
-      <c r="AG287" t="s">
+      <c r="AG290" t="s">
         <v>156</v>
       </c>
-      <c r="AH287" t="s">
+      <c r="AH290" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="288" spans="24:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y288" s="41"/>
-      <c r="AF288">
+    <row r="291" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y291" s="41"/>
+      <c r="AF291">
         <f>O59-500</f>
         <v>10.76400000000001</v>
       </c>
-      <c r="AG288" s="17">
+      <c r="AG291" s="17">
         <f>X59-V59</f>
         <v>76</v>
       </c>
-      <c r="AH288" s="17">
-        <f>AG288*AF288</f>
+      <c r="AH291" s="17">
+        <f>AG291*AF291</f>
         <v>818.06400000000076</v>
       </c>
     </row>
-    <row r="289" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Y289" s="41"/>
-      <c r="AF289">
+    <row r="292" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y292" s="41"/>
+      <c r="AF292">
         <f>O60-500</f>
         <v>10.338999999999999</v>
       </c>
-      <c r="AG289" s="17">
+      <c r="AG292" s="17">
         <f>X60-V60</f>
         <v>76</v>
       </c>
-      <c r="AH289" s="17">
-        <f t="shared" ref="AH289:AH294" si="91">AG289*AF289</f>
+      <c r="AH292" s="17">
+        <f t="shared" ref="AH292:AH297" si="92">AG292*AF292</f>
         <v>785.7639999999999</v>
       </c>
     </row>
-    <row r="290" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AF290">
+    <row r="293" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF293">
         <f>O61-500</f>
         <v>9.6879999999999882</v>
       </c>
-      <c r="AG290" s="17">
+      <c r="AG293" s="17">
         <f>X61-V61</f>
         <v>76</v>
       </c>
-      <c r="AH290" s="17">
-        <f t="shared" si="91"/>
+      <c r="AH293" s="17">
+        <f t="shared" si="92"/>
         <v>736.2879999999991</v>
-      </c>
-    </row>
-    <row r="291" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AE291" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF291">
-        <f>O62-500</f>
-        <v>10.899999999999977</v>
-      </c>
-      <c r="AG291" s="17">
-        <f>X62-V62</f>
-        <v>91</v>
-      </c>
-      <c r="AH291" s="17">
-        <f t="shared" si="91"/>
-        <v>991.89999999999793</v>
-      </c>
-    </row>
-    <row r="292" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AE292" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF292">
-        <f>O63-500</f>
-        <v>10.899999999999977</v>
-      </c>
-      <c r="AG292" s="17">
-        <f>X63-V63</f>
-        <v>91</v>
-      </c>
-      <c r="AH292" s="17">
-        <f t="shared" si="91"/>
-        <v>991.89999999999793</v>
-      </c>
-    </row>
-    <row r="293" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AE293" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF293">
-        <f>O64-500</f>
-        <v>10.899999999999977</v>
-      </c>
-      <c r="AG293" s="17">
-        <f>X64-V64</f>
-        <v>91</v>
-      </c>
-      <c r="AH293" s="17">
-        <f t="shared" si="91"/>
-        <v>991.89999999999793</v>
       </c>
     </row>
     <row r="294" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,474 +21072,525 @@
         <v>157</v>
       </c>
       <c r="AF294">
+        <f>O62-500</f>
+        <v>10.899999999999977</v>
+      </c>
+      <c r="AG294" s="17">
+        <f>X62-V62</f>
+        <v>91</v>
+      </c>
+      <c r="AH294" s="17">
+        <f t="shared" si="92"/>
+        <v>991.89999999999793</v>
+      </c>
+    </row>
+    <row r="295" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE295" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF295">
+        <f>O63-500</f>
+        <v>10.899999999999977</v>
+      </c>
+      <c r="AG295" s="17">
+        <f>X63-V63</f>
+        <v>91</v>
+      </c>
+      <c r="AH295" s="17">
+        <f t="shared" si="92"/>
+        <v>991.89999999999793</v>
+      </c>
+    </row>
+    <row r="296" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE296" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF296">
+        <f>O64-500</f>
+        <v>10.899999999999977</v>
+      </c>
+      <c r="AG296" s="17">
+        <f>X64-V64</f>
+        <v>91</v>
+      </c>
+      <c r="AH296" s="17">
+        <f t="shared" si="92"/>
+        <v>991.89999999999793</v>
+      </c>
+    </row>
+    <row r="297" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE297" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF297">
         <f>O65-300</f>
         <v>6.5400000000000205</v>
       </c>
-      <c r="AG294" s="17">
+      <c r="AG297" s="17">
         <f>X65-V65</f>
         <v>91</v>
       </c>
-      <c r="AH294" s="17">
-        <f t="shared" si="91"/>
+      <c r="AH297" s="17">
+        <f t="shared" si="92"/>
         <v>595.14000000000192</v>
       </c>
     </row>
-    <row r="295" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AF295" t="s">
+    <row r="298" spans="25:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF298" t="s">
         <v>17</v>
       </c>
-      <c r="AH295" s="17" t="s">
+      <c r="AH298" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF296">
-        <f>SUM(AF288:AF294)</f>
+    <row r="299" spans="25:40" x14ac:dyDescent="0.2">
+      <c r="AF299">
+        <f>SUM(AF291:AF297)</f>
         <v>70.030999999999949</v>
       </c>
-      <c r="AH296" s="47">
-        <f>SUM(AH288:AH294)</f>
+      <c r="AH299" s="47">
+        <f>SUM(AH291:AH297)</f>
         <v>5910.9559999999956</v>
       </c>
     </row>
-    <row r="297" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF297" s="55" t="s">
+    <row r="300" spans="25:40" x14ac:dyDescent="0.2">
+      <c r="AF300" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AG297" s="55"/>
-      <c r="AH297" s="55"/>
-    </row>
-    <row r="300" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF300" s="41" t="s">
+      <c r="AG300" s="55"/>
+      <c r="AH300" s="55"/>
+    </row>
+    <row r="303" spans="25:40" x14ac:dyDescent="0.2">
+      <c r="AF303" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="AM300" s="41" t="s">
+      <c r="AM303" s="41" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF301" t="s">
+    <row r="304" spans="25:40" x14ac:dyDescent="0.2">
+      <c r="AF304" t="s">
         <v>137</v>
       </c>
-      <c r="AG301">
+      <c r="AG304">
         <v>4300</v>
       </c>
-      <c r="AM301" t="s">
+      <c r="AM304" t="s">
         <v>137</v>
       </c>
-      <c r="AN301">
+      <c r="AN304">
         <v>4300</v>
       </c>
     </row>
-    <row r="302" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF302" t="s">
+    <row r="305" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF305" t="s">
         <v>138</v>
       </c>
-      <c r="AG302">
+      <c r="AG305">
         <f>O76</f>
         <v>4248.7540000000008</v>
       </c>
-      <c r="AM302" t="s">
+      <c r="AM305" t="s">
         <v>138</v>
       </c>
-      <c r="AN302">
-        <f>AG302</f>
+      <c r="AN305">
+        <f>AG305</f>
         <v>4248.7540000000008</v>
       </c>
     </row>
-    <row r="303" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF303" t="s">
+    <row r="306" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF306" t="s">
         <v>139</v>
       </c>
-      <c r="AG303">
-        <f>AG302-AG301</f>
+      <c r="AG306">
+        <f>AG305-AG304</f>
         <v>-51.245999999999185</v>
-      </c>
-    </row>
-    <row r="304" spans="25:40" x14ac:dyDescent="0.2">
-      <c r="AF304" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG304" s="15">
-        <v>705</v>
-      </c>
-      <c r="AM304" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN304" s="43">
-        <f>SUM(AF254:AF257)+190000</f>
-        <v>2718000</v>
-      </c>
-    </row>
-    <row r="305" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF305" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG305" s="44">
-        <f>AG303*AG304</f>
-        <v>-36128.429999999425</v>
-      </c>
-      <c r="AM305" t="s">
-        <v>147</v>
-      </c>
-      <c r="AN305" s="17">
-        <f>W76</f>
-        <v>2689678.5019999999</v>
-      </c>
-    </row>
-    <row r="306" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM306" t="s">
-        <v>148</v>
-      </c>
-      <c r="AN306" s="45">
-        <f>AN304-AN305</f>
-        <v>28321.498000000138</v>
       </c>
     </row>
     <row r="307" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF307" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AG307" s="15">
-        <v>3031500</v>
+        <v>705</v>
+      </c>
+      <c r="AM307" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN307" s="43">
+        <f>SUM(AF257:AF260)+190000</f>
+        <v>2718000</v>
       </c>
     </row>
     <row r="308" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AF308" t="s">
         <v>141</v>
       </c>
-      <c r="AG308" s="17">
+      <c r="AG308" s="44">
+        <f>AG306*AG307</f>
+        <v>-36128.429999999425</v>
+      </c>
+      <c r="AM308" t="s">
+        <v>147</v>
+      </c>
+      <c r="AN308" s="17">
+        <f>W76</f>
+        <v>2689678.5019999999</v>
+      </c>
+    </row>
+    <row r="309" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM309" t="s">
+        <v>148</v>
+      </c>
+      <c r="AN309" s="45">
+        <f>AN307-AN308</f>
+        <v>28321.498000000138</v>
+      </c>
+    </row>
+    <row r="310" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF310" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG310" s="15">
+        <v>3031500</v>
+      </c>
+    </row>
+    <row r="311" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF311" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG311" s="17">
         <f>AC76</f>
         <v>2995371.57</v>
       </c>
-      <c r="AM308" s="41" t="s">
+      <c r="AM311" s="41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="309" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF309" t="s">
+    <row r="312" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF312" t="s">
         <v>139</v>
       </c>
-      <c r="AG309" s="44">
-        <f>AG308-AG307</f>
+      <c r="AG312" s="44">
+        <f>AG311-AG310</f>
         <v>-36128.430000000168</v>
       </c>
-      <c r="AM309" t="s">
+      <c r="AM312" t="s">
         <v>137</v>
       </c>
-      <c r="AN309">
+      <c r="AN312">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="310" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM310" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN310">
-        <f>AN302</f>
-        <v>4248.7540000000008</v>
-      </c>
-    </row>
-    <row r="311" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF311" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG311" s="47">
-        <f>AG284+AG309</f>
-        <v>16744.975000000093</v>
-      </c>
-    </row>
-    <row r="312" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM312" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN312" s="43">
-        <f>AN304</f>
-        <v>2718000</v>
       </c>
     </row>
     <row r="313" spans="32:40" x14ac:dyDescent="0.2">
       <c r="AM313" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN313">
+        <f>AN305</f>
+        <v>4248.7540000000008</v>
+      </c>
+    </row>
+    <row r="314" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF314" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG314" s="47">
+        <f>AG287+AG312</f>
+        <v>16744.975000000093</v>
+      </c>
+    </row>
+    <row r="315" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM315" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN315" s="43">
+        <f>AN307</f>
+        <v>2718000</v>
+      </c>
+    </row>
+    <row r="316" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM316" t="s">
         <v>147</v>
       </c>
-      <c r="AN313" s="17">
+      <c r="AN316" s="17">
         <f>W67+W68+W69+W70+W71+W72+W73+(O74*668)+(O75*668)</f>
         <v>2716213.4279999998</v>
       </c>
     </row>
-    <row r="314" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AM314" t="s">
+    <row r="317" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AM317" t="s">
         <v>148</v>
       </c>
-      <c r="AN314" s="45">
-        <f>AN312-AN313</f>
+      <c r="AN317" s="45">
+        <f>AN315-AN316</f>
         <v>1786.5720000001602</v>
       </c>
     </row>
-    <row r="316" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF316" t="s">
+    <row r="319" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF319" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="317" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF317" t="s">
+    <row r="320" spans="32:40" x14ac:dyDescent="0.2">
+      <c r="AF320" t="s">
         <v>155</v>
       </c>
-      <c r="AG317" t="s">
+      <c r="AG320" t="s">
         <v>156</v>
       </c>
-      <c r="AH317" t="s">
+      <c r="AH320" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="318" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF318">
+    <row r="321" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF321">
         <f>O67-500</f>
         <v>11.160000000000025</v>
       </c>
-      <c r="AG318" s="17">
+      <c r="AG321" s="17">
         <f>X67-V67</f>
         <v>73</v>
       </c>
-      <c r="AH318" s="17">
-        <f>AF318*AG318</f>
+      <c r="AH321" s="17">
+        <f>AF321*AG321</f>
         <v>814.68000000000188</v>
       </c>
     </row>
-    <row r="319" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF319">
+    <row r="322" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF322">
         <f>O68-500</f>
         <v>9.1940000000000168</v>
       </c>
-      <c r="AG319" s="17">
+      <c r="AG322" s="17">
         <f>X68-V68</f>
         <v>73</v>
       </c>
-      <c r="AH319" s="17">
-        <f t="shared" ref="AH319:AH326" si="92">AF319*AG319</f>
+      <c r="AH322" s="17">
+        <f t="shared" ref="AH322:AH329" si="93">AF322*AG322</f>
         <v>671.16200000000117</v>
       </c>
     </row>
-    <row r="320" spans="32:40" x14ac:dyDescent="0.2">
-      <c r="AF320">
+    <row r="323" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF323">
         <f>O69-500</f>
         <v>-14.966999999999985</v>
       </c>
-      <c r="AG320" s="17">
+      <c r="AG323" s="17">
         <f>X69-V69</f>
         <v>73</v>
       </c>
-      <c r="AH320" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH323" s="17">
+        <f t="shared" si="93"/>
         <v>-1092.590999999999</v>
       </c>
     </row>
-    <row r="321" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF321">
+    <row r="324" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF324">
         <f>O70-500</f>
         <v>10.379999999999995</v>
       </c>
-      <c r="AG321" s="17">
+      <c r="AG324" s="17">
         <f>X70-V70</f>
         <v>73</v>
       </c>
-      <c r="AH321" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH324" s="17">
+        <f t="shared" si="93"/>
         <v>757.73999999999967</v>
       </c>
     </row>
-    <row r="322" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF322">
+    <row r="325" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF325">
         <f>O71-500</f>
         <v>-15.939000000000021</v>
       </c>
-      <c r="AG322" s="17">
+      <c r="AG325" s="17">
         <f>X71-V71</f>
         <v>71</v>
       </c>
-      <c r="AH322" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH325" s="17">
+        <f t="shared" si="93"/>
         <v>-1131.6690000000015</v>
       </c>
     </row>
-    <row r="323" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF323">
+    <row r="326" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF326">
         <f>O72-500</f>
         <v>-15.386000000000024</v>
       </c>
-      <c r="AG323" s="17">
+      <c r="AG326" s="17">
         <f>X72-V72</f>
         <v>71</v>
       </c>
-      <c r="AH323" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH326" s="17">
+        <f t="shared" si="93"/>
         <v>-1092.4060000000018</v>
       </c>
     </row>
-    <row r="324" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF324">
+    <row r="327" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF327">
         <f>O73-500</f>
         <v>-16.12700000000001</v>
       </c>
-      <c r="AG324" s="17">
+      <c r="AG327" s="17">
         <f>X73-V73</f>
         <v>71</v>
       </c>
-      <c r="AH324" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH327" s="17">
+        <f t="shared" si="93"/>
         <v>-1145.0170000000007</v>
       </c>
     </row>
-    <row r="325" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF325">
+    <row r="328" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF328">
         <f>O74-500</f>
         <v>-17.918999999999983</v>
       </c>
-      <c r="AG325" s="17">
+      <c r="AG328" s="17">
         <f>X74-V74</f>
         <v>71</v>
       </c>
-      <c r="AH325" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH328" s="17">
+        <f t="shared" si="93"/>
         <v>-1272.2489999999989</v>
       </c>
     </row>
-    <row r="326" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF326">
+    <row r="329" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF329">
         <f>O75-300</f>
         <v>-1.6419999999999959</v>
       </c>
-      <c r="AG326" s="17">
+      <c r="AG329" s="17">
         <f>X75-V75</f>
         <v>71</v>
       </c>
-      <c r="AH326" s="17">
-        <f t="shared" si="92"/>
+      <c r="AH329" s="17">
+        <f t="shared" si="93"/>
         <v>-116.58199999999971</v>
       </c>
     </row>
-    <row r="327" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF327" t="s">
+    <row r="330" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF330" t="s">
         <v>17</v>
       </c>
-      <c r="AH327" s="17" t="s">
+      <c r="AH330" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="328" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF328">
-        <f>SUM(AF318:AF326)</f>
+    <row r="331" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF331">
+        <f>SUM(AF321:AF329)</f>
         <v>-51.245999999999981</v>
       </c>
-      <c r="AH328" s="47">
-        <f>SUM(AH318:AH326)</f>
+      <c r="AH331" s="47">
+        <f>SUM(AH321:AH329)</f>
         <v>-3606.9319999999993</v>
       </c>
     </row>
-    <row r="329" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF329" s="55" t="s">
+    <row r="332" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF332" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="AG329" s="55"/>
-      <c r="AH329" s="55"/>
-    </row>
-    <row r="333" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF333" s="56" t="s">
+      <c r="AG332" s="55"/>
+      <c r="AH332" s="55"/>
+    </row>
+    <row r="336" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF336" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="AG333" s="56"/>
-      <c r="AI333" s="55" t="s">
+      <c r="AG336" s="56"/>
+      <c r="AI336" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="AJ333" s="55"/>
-      <c r="AK333" s="46"/>
-      <c r="AL333" s="46"/>
-    </row>
-    <row r="334" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF334" t="s">
+      <c r="AJ336" s="55"/>
+      <c r="AK336" s="46"/>
+      <c r="AL336" s="46"/>
+    </row>
+    <row r="337" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF337" t="s">
         <v>137</v>
       </c>
-      <c r="AG334">
+      <c r="AG337">
         <f>O83</f>
         <v>548.89300000000003</v>
       </c>
-      <c r="AI334" t="s">
+      <c r="AI337" t="s">
         <v>152</v>
       </c>
-      <c r="AJ334">
+      <c r="AJ337">
         <v>500</v>
       </c>
-    </row>
-    <row r="335" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF335" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG335">
-        <f>AG334</f>
-        <v>548.89300000000003</v>
-      </c>
-      <c r="AI335" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ335">
-        <f>AG335</f>
-        <v>548.89300000000003</v>
-      </c>
-    </row>
-    <row r="336" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF336" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG336">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AF337" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG337">
-        <v>800</v>
-      </c>
-      <c r="AI337" t="s">
-        <v>136</v>
-      </c>
-      <c r="AJ337" s="43">
-        <f>AF253</f>
-        <v>325000</v>
-      </c>
-      <c r="AK337" s="43"/>
-      <c r="AL337" s="43"/>
     </row>
     <row r="338" spans="32:38" x14ac:dyDescent="0.2">
       <c r="AF338" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG338">
+        <f>AG337</f>
+        <v>548.89300000000003</v>
+      </c>
+      <c r="AI338" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ338">
+        <f>AG338</f>
+        <v>548.89300000000003</v>
+      </c>
+    </row>
+    <row r="339" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF339" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF340" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG340">
+        <v>800</v>
+      </c>
+      <c r="AI340" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ340" s="43">
+        <f>AF256</f>
+        <v>325000</v>
+      </c>
+      <c r="AK340" s="43"/>
+      <c r="AL340" s="43"/>
+    </row>
+    <row r="341" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AF341" t="s">
         <v>141</v>
       </c>
-      <c r="AG338" s="15">
-        <f>AG335*AG337</f>
+      <c r="AG341" s="15">
+        <f>AG338*AG340</f>
         <v>439114.4</v>
       </c>
-      <c r="AI338" t="s">
+      <c r="AI341" t="s">
         <v>153</v>
       </c>
-      <c r="AJ338" s="17">
+      <c r="AJ341" s="17">
         <f>W83</f>
         <v>356780.45</v>
       </c>
-      <c r="AK338" s="17"/>
-      <c r="AL338" s="17"/>
-    </row>
-    <row r="339" spans="32:38" x14ac:dyDescent="0.2">
-      <c r="AI339" t="s">
+      <c r="AK341" s="17"/>
+      <c r="AL341" s="17"/>
+    </row>
+    <row r="342" spans="32:38" x14ac:dyDescent="0.2">
+      <c r="AI342" t="s">
         <v>148</v>
       </c>
-      <c r="AJ339" s="45">
-        <f>AJ337-AJ338</f>
+      <c r="AJ342" s="45">
+        <f>AJ340-AJ341</f>
         <v>-31780.450000000012</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="L58:AD58"/>
     <mergeCell ref="AF61:AH61"/>
     <mergeCell ref="K39:K45"/>
@@ -20362,17 +21598,16 @@
     <mergeCell ref="K19:K22"/>
     <mergeCell ref="K32:K37"/>
     <mergeCell ref="K47:K52"/>
-    <mergeCell ref="AF218:AJ218"/>
-    <mergeCell ref="AF274:AG274"/>
-    <mergeCell ref="AM274:AN274"/>
-    <mergeCell ref="AI333:AJ333"/>
-    <mergeCell ref="AF333:AG333"/>
-    <mergeCell ref="AF297:AH297"/>
-    <mergeCell ref="AF329:AH329"/>
-    <mergeCell ref="AI274:AK274"/>
-    <mergeCell ref="AD268:AH268"/>
-    <mergeCell ref="AC201:AD201"/>
-    <mergeCell ref="AC206:AD206"/>
+    <mergeCell ref="AF221:AJ221"/>
+    <mergeCell ref="AF277:AG277"/>
+    <mergeCell ref="AM277:AN277"/>
+    <mergeCell ref="AI336:AJ336"/>
+    <mergeCell ref="AF336:AG336"/>
+    <mergeCell ref="AF300:AH300"/>
+    <mergeCell ref="AF332:AH332"/>
+    <mergeCell ref="AI277:AK277"/>
+    <mergeCell ref="AD271:AH271"/>
+    <mergeCell ref="AC209:AD209"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20421,9 +21656,9 @@
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" s="113">
+        <v>344</v>
+      </c>
+      <c r="D9" s="112">
         <f>D7-D8</f>
         <v>600</v>
       </c>
@@ -20477,25 +21712,25 @@
       <c r="C19" s="82" t="s">
         <v>349</v>
       </c>
-      <c r="D19" s="116">
+      <c r="D19" s="115">
         <v>0.03</v>
       </c>
-      <c r="E19" s="116">
+      <c r="E19" s="115">
         <v>0.05</v>
       </c>
-      <c r="F19" s="117">
+      <c r="F19" s="116">
         <v>5.5E-2</v>
       </c>
-      <c r="G19" s="116">
+      <c r="G19" s="115">
         <v>0.06</v>
       </c>
-      <c r="H19" s="117">
+      <c r="H19" s="116">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I19" s="116">
+      <c r="I19" s="115">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J19" s="116">
+      <c r="J19" s="115">
         <v>0.08</v>
       </c>
     </row>
@@ -20617,25 +21852,25 @@
       <c r="C25" s="82" t="s">
         <v>349</v>
       </c>
-      <c r="D25" s="116">
+      <c r="D25" s="115">
         <v>0.03</v>
       </c>
-      <c r="E25" s="116">
+      <c r="E25" s="115">
         <v>0.05</v>
       </c>
-      <c r="F25" s="117">
+      <c r="F25" s="116">
         <v>5.5E-2</v>
       </c>
-      <c r="G25" s="116">
+      <c r="G25" s="115">
         <v>0.06</v>
       </c>
-      <c r="H25" s="117">
+      <c r="H25" s="116">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I25" s="116">
+      <c r="I25" s="115">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J25" s="116">
+      <c r="J25" s="115">
         <v>0.08</v>
       </c>
     </row>
@@ -20737,7 +21972,7 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C32" s="114"/>
+      <c r="C32" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20760,33 +21995,33 @@
   <sheetData>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="C4" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="D4" s="82" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="82" t="s">
+      <c r="G4" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="F4" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="G4" s="82" t="s">
-        <v>312</v>
-      </c>
       <c r="I4" s="107" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" s="52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D5" s="52">
         <v>19</v>
@@ -20805,10 +22040,10 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="52" t="s">
         <v>319</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>318</v>
       </c>
       <c r="D6" s="52">
         <v>19</v>
@@ -20827,10 +22062,10 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" s="52" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D7" s="52">
         <v>19</v>
@@ -20849,10 +22084,10 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" s="52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D8" s="52">
         <v>19</v>
@@ -20871,43 +22106,43 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="D10" s="82" t="s">
-        <v>328</v>
-      </c>
-      <c r="E10" s="82" t="s">
+      <c r="G10" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="F10" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="G10" s="82" t="s">
-        <v>312</v>
-      </c>
       <c r="H10" s="109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I10" s="43"/>
       <c r="K10" s="108" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L10" s="108" t="s">
         <v>244</v>
       </c>
       <c r="M10" s="108" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" s="52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D11" s="52">
         <v>19</v>
@@ -20945,10 +22180,10 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="52" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D12" s="52">
         <v>19</v>
@@ -20986,10 +22221,10 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" s="52" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D13" s="52">
         <v>19</v>
@@ -21027,10 +22262,10 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" s="52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D14" s="52">
         <v>19</v>
@@ -21073,35 +22308,35 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="82" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>329</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="C16" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="D16" s="82" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" s="82" t="s">
+      <c r="G16" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="F16" s="82" t="s">
-        <v>314</v>
-      </c>
-      <c r="G16" s="82" t="s">
-        <v>312</v>
-      </c>
       <c r="H16" s="109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K16" s="43"/>
       <c r="M16" s="43"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D17" s="52">
         <v>19</v>
@@ -21139,10 +22374,10 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="52" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D18" s="52">
         <v>19</v>
@@ -21180,10 +22415,10 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="52" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D19" s="52">
         <v>19</v>
@@ -21221,10 +22456,10 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D20" s="52">
         <v>19</v>
@@ -21401,7 +22636,7 @@
         <v>12900</v>
       </c>
       <c r="F21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -21412,7 +22647,7 @@
         <v>7000</v>
       </c>
       <c r="F22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -21464,8 +22699,8 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="121" t="s">
-        <v>380</v>
+      <c r="B31" s="120" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
